--- a/Data/ID_Generators/POLAND_IDGenerator.xlsx
+++ b/Data/ID_Generators/POLAND_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\ID_Generators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9DB585-E31C-4326-ADDE-F5C9B808482B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5A8241-A676-4F19-95B9-652EB274964A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="219">
   <si>
     <t>Country1</t>
   </si>
@@ -483,6 +483,216 @@
   </si>
   <si>
     <t>GHE456310</t>
+  </si>
+  <si>
+    <t>GHE456311</t>
+  </si>
+  <si>
+    <t>GHE456312</t>
+  </si>
+  <si>
+    <t>GHE456313</t>
+  </si>
+  <si>
+    <t>GHE456314</t>
+  </si>
+  <si>
+    <t>GHE456315</t>
+  </si>
+  <si>
+    <t>GHE456316</t>
+  </si>
+  <si>
+    <t>GHE456317</t>
+  </si>
+  <si>
+    <t>GHE456318</t>
+  </si>
+  <si>
+    <t>GHE456319</t>
+  </si>
+  <si>
+    <t>GHE456320</t>
+  </si>
+  <si>
+    <t>GHE456321</t>
+  </si>
+  <si>
+    <t>GHE456322</t>
+  </si>
+  <si>
+    <t>GHE456323</t>
+  </si>
+  <si>
+    <t>GHE456324</t>
+  </si>
+  <si>
+    <t>GHE456325</t>
+  </si>
+  <si>
+    <t>GHE456326</t>
+  </si>
+  <si>
+    <t>GHE456327</t>
+  </si>
+  <si>
+    <t>GHE456328</t>
+  </si>
+  <si>
+    <t>GHE456329</t>
+  </si>
+  <si>
+    <t>GHE456330</t>
+  </si>
+  <si>
+    <t>GHE456331</t>
+  </si>
+  <si>
+    <t>GHE456332</t>
+  </si>
+  <si>
+    <t>GHE456333</t>
+  </si>
+  <si>
+    <t>GHE456334</t>
+  </si>
+  <si>
+    <t>GHE456335</t>
+  </si>
+  <si>
+    <t>GHE456336</t>
+  </si>
+  <si>
+    <t>GHE456337</t>
+  </si>
+  <si>
+    <t>GHE456338</t>
+  </si>
+  <si>
+    <t>GHE456339</t>
+  </si>
+  <si>
+    <t>GHE456340</t>
+  </si>
+  <si>
+    <t>GHE456341</t>
+  </si>
+  <si>
+    <t>GHE456342</t>
+  </si>
+  <si>
+    <t>GHE456343</t>
+  </si>
+  <si>
+    <t>GHE456344</t>
+  </si>
+  <si>
+    <t>GHE456345</t>
+  </si>
+  <si>
+    <t>GHE456346</t>
+  </si>
+  <si>
+    <t>GHE456347</t>
+  </si>
+  <si>
+    <t>GHE456348</t>
+  </si>
+  <si>
+    <t>GHE456349</t>
+  </si>
+  <si>
+    <t>GHE456350</t>
+  </si>
+  <si>
+    <t>GHE456351</t>
+  </si>
+  <si>
+    <t>GHE456352</t>
+  </si>
+  <si>
+    <t>GHE456353</t>
+  </si>
+  <si>
+    <t>GHE456354</t>
+  </si>
+  <si>
+    <t>GHE456355</t>
+  </si>
+  <si>
+    <t>GHE456356</t>
+  </si>
+  <si>
+    <t>GHE456357</t>
+  </si>
+  <si>
+    <t>GHE456358</t>
+  </si>
+  <si>
+    <t>GHE456359</t>
+  </si>
+  <si>
+    <t>GHE456360</t>
+  </si>
+  <si>
+    <t>GHE456361</t>
+  </si>
+  <si>
+    <t>GHE456362</t>
+  </si>
+  <si>
+    <t>GHE456363</t>
+  </si>
+  <si>
+    <t>GHE456364</t>
+  </si>
+  <si>
+    <t>GHE456365</t>
+  </si>
+  <si>
+    <t>GHE456366</t>
+  </si>
+  <si>
+    <t>GHE456367</t>
+  </si>
+  <si>
+    <t>GHE456368</t>
+  </si>
+  <si>
+    <t>GHE456369</t>
+  </si>
+  <si>
+    <t>GHE456370</t>
+  </si>
+  <si>
+    <t>GHE456371</t>
+  </si>
+  <si>
+    <t>GHE456372</t>
+  </si>
+  <si>
+    <t>GHE456373</t>
+  </si>
+  <si>
+    <t>GHE456374</t>
+  </si>
+  <si>
+    <t>GHE456375</t>
+  </si>
+  <si>
+    <t>GHE456376</t>
+  </si>
+  <si>
+    <t>GHE456377</t>
+  </si>
+  <si>
+    <t>GHE456378</t>
+  </si>
+  <si>
+    <t>GHE456379</t>
+  </si>
+  <si>
+    <t>GHE456380</t>
   </si>
 </sst>
 </file>
@@ -893,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:N450"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="15.33203125" customWidth="1"/>
@@ -5994,7 +6204,7 @@
         <v>456305</v>
       </c>
       <c r="N131" t="str">
-        <f t="shared" ref="N131:N136" si="2">K131&amp;L131</f>
+        <f t="shared" ref="N131:N194" si="2">K131&amp;L131</f>
         <v>GHE456305</v>
       </c>
     </row>
@@ -6191,6 +6401,7616 @@
       <c r="N136" t="str">
         <f t="shared" si="2"/>
         <v>GHE456310</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="6">
+        <v>9893790861</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="5">
+        <v>47678965531</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I137" t="s">
+        <v>149</v>
+      </c>
+      <c r="K137" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L137">
+        <v>456311</v>
+      </c>
+      <c r="N137" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456311</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A138" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" s="6">
+        <v>9893790862</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="5">
+        <v>47678965532</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I138" t="s">
+        <v>150</v>
+      </c>
+      <c r="K138" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L138">
+        <v>456312</v>
+      </c>
+      <c r="N138" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456312</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C139" s="6">
+        <v>9893790863</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="5">
+        <v>47678965533</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I139" t="s">
+        <v>151</v>
+      </c>
+      <c r="K139" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L139">
+        <v>456313</v>
+      </c>
+      <c r="N139" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456313</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A140" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C140" s="6">
+        <v>9893790864</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="5">
+        <v>47678965534</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I140" t="s">
+        <v>152</v>
+      </c>
+      <c r="K140" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L140">
+        <v>456314</v>
+      </c>
+      <c r="N140" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456314</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A141" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" s="6">
+        <v>9893790865</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="5">
+        <v>47678965535</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I141" t="s">
+        <v>153</v>
+      </c>
+      <c r="K141" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L141">
+        <v>456315</v>
+      </c>
+      <c r="N141" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456315</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A142" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="6">
+        <v>9893790866</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="5">
+        <v>47678965536</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I142" t="s">
+        <v>154</v>
+      </c>
+      <c r="K142" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L142">
+        <v>456316</v>
+      </c>
+      <c r="N142" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456316</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A143" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="6">
+        <v>9893790867</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="5">
+        <v>47678965537</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I143" t="s">
+        <v>155</v>
+      </c>
+      <c r="K143" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L143">
+        <v>456317</v>
+      </c>
+      <c r="N143" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456317</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A144" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="6">
+        <v>9893790868</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="5">
+        <v>47678965538</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I144" t="s">
+        <v>156</v>
+      </c>
+      <c r="K144" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L144">
+        <v>456318</v>
+      </c>
+      <c r="N144" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456318</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A145" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="6">
+        <v>9893790869</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="5">
+        <v>47678965539</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" t="s">
+        <v>157</v>
+      </c>
+      <c r="K145" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L145">
+        <v>456319</v>
+      </c>
+      <c r="N145" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456319</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A146" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="6">
+        <v>9893790870</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="5">
+        <v>47678965540</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I146" t="s">
+        <v>158</v>
+      </c>
+      <c r="K146" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L146">
+        <v>456320</v>
+      </c>
+      <c r="N146" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456320</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A147" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="6">
+        <v>9893790871</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="5">
+        <v>47678965541</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" t="s">
+        <v>159</v>
+      </c>
+      <c r="K147" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L147">
+        <v>456321</v>
+      </c>
+      <c r="N147" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456321</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A148" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148" s="6">
+        <v>9893790872</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="5">
+        <v>47678965542</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I148" t="s">
+        <v>160</v>
+      </c>
+      <c r="K148" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L148">
+        <v>456322</v>
+      </c>
+      <c r="N148" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456322</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A149" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="6">
+        <v>9893790873</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="5">
+        <v>47678965543</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I149" t="s">
+        <v>161</v>
+      </c>
+      <c r="K149" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L149">
+        <v>456323</v>
+      </c>
+      <c r="N149" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456323</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A150" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150" s="6">
+        <v>9893790874</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="5">
+        <v>47678965544</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I150" t="s">
+        <v>162</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L150">
+        <v>456324</v>
+      </c>
+      <c r="N150" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456324</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="6">
+        <v>9893790875</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="5">
+        <v>47678965545</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H151" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I151" t="s">
+        <v>163</v>
+      </c>
+      <c r="K151" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L151">
+        <v>456325</v>
+      </c>
+      <c r="N151" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456325</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152" s="6">
+        <v>9893790876</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="5">
+        <v>47678965546</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I152" t="s">
+        <v>164</v>
+      </c>
+      <c r="K152" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L152">
+        <v>456326</v>
+      </c>
+      <c r="N152" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456326</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" s="6">
+        <v>9893790877</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="5">
+        <v>47678965547</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" t="s">
+        <v>165</v>
+      </c>
+      <c r="K153" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L153">
+        <v>456327</v>
+      </c>
+      <c r="N153" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456327</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" s="6">
+        <v>9893790878</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="5">
+        <v>47678965548</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I154" t="s">
+        <v>166</v>
+      </c>
+      <c r="K154" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L154">
+        <v>456328</v>
+      </c>
+      <c r="N154" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456328</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" s="6">
+        <v>9893790879</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="5">
+        <v>47678965549</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155" t="s">
+        <v>167</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L155">
+        <v>456329</v>
+      </c>
+      <c r="N155" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456329</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" s="6">
+        <v>9893790880</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="5">
+        <v>47678965550</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I156" t="s">
+        <v>168</v>
+      </c>
+      <c r="K156" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L156">
+        <v>456330</v>
+      </c>
+      <c r="N156" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456330</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="6">
+        <v>9893790881</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="5">
+        <v>47678965551</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I157" t="s">
+        <v>169</v>
+      </c>
+      <c r="K157" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L157">
+        <v>456331</v>
+      </c>
+      <c r="N157" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456331</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C158" s="6">
+        <v>9893790882</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="5">
+        <v>47678965552</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I158" t="s">
+        <v>170</v>
+      </c>
+      <c r="K158" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L158">
+        <v>456332</v>
+      </c>
+      <c r="N158" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456332</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" s="6">
+        <v>9893790883</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="5">
+        <v>47678965553</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I159" t="s">
+        <v>171</v>
+      </c>
+      <c r="K159" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L159">
+        <v>456333</v>
+      </c>
+      <c r="N159" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456333</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" s="6">
+        <v>9893790884</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="5">
+        <v>47678965554</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I160" t="s">
+        <v>172</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L160">
+        <v>456334</v>
+      </c>
+      <c r="N160" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456334</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" s="6">
+        <v>9893790885</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="5">
+        <v>47678965555</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I161" t="s">
+        <v>173</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L161">
+        <v>456335</v>
+      </c>
+      <c r="N161" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456335</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" s="6">
+        <v>9893790886</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="5">
+        <v>47678965556</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162" t="s">
+        <v>174</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L162">
+        <v>456336</v>
+      </c>
+      <c r="N162" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456336</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" s="6">
+        <v>9893790887</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="5">
+        <v>47678965557</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I163" t="s">
+        <v>175</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L163">
+        <v>456337</v>
+      </c>
+      <c r="N163" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456337</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" s="6">
+        <v>9893790888</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="5">
+        <v>47678965558</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164" t="s">
+        <v>176</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L164">
+        <v>456338</v>
+      </c>
+      <c r="N164" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456338</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" s="6">
+        <v>9893790889</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="5">
+        <v>47678965559</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I165" t="s">
+        <v>177</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L165">
+        <v>456339</v>
+      </c>
+      <c r="N165" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456339</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166" s="6">
+        <v>9893790890</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="5">
+        <v>47678965560</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I166" t="s">
+        <v>178</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L166">
+        <v>456340</v>
+      </c>
+      <c r="N166" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456340</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167" s="6">
+        <v>9893790891</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="5">
+        <v>47678965561</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167" t="s">
+        <v>179</v>
+      </c>
+      <c r="K167" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L167">
+        <v>456341</v>
+      </c>
+      <c r="N167" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456341</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="6">
+        <v>9893790892</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="5">
+        <v>47678965562</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I168" t="s">
+        <v>180</v>
+      </c>
+      <c r="K168" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L168">
+        <v>456342</v>
+      </c>
+      <c r="N168" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456342</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169" s="6">
+        <v>9893790893</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="5">
+        <v>47678965563</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" t="s">
+        <v>181</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L169">
+        <v>456343</v>
+      </c>
+      <c r="N169" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456343</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" s="6">
+        <v>9893790894</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="5">
+        <v>47678965564</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I170" t="s">
+        <v>182</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L170">
+        <v>456344</v>
+      </c>
+      <c r="N170" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456344</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" s="6">
+        <v>9893790895</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="5">
+        <v>47678965565</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I171" t="s">
+        <v>183</v>
+      </c>
+      <c r="K171" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L171">
+        <v>456345</v>
+      </c>
+      <c r="N171" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456345</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="6">
+        <v>9893790896</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="5">
+        <v>47678965566</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I172" t="s">
+        <v>184</v>
+      </c>
+      <c r="K172" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L172">
+        <v>456346</v>
+      </c>
+      <c r="N172" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456346</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" s="6">
+        <v>9893790897</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="5">
+        <v>47678965567</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I173" t="s">
+        <v>185</v>
+      </c>
+      <c r="K173" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L173">
+        <v>456347</v>
+      </c>
+      <c r="N173" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456347</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174" s="6">
+        <v>9893790898</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="5">
+        <v>47678965568</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I174" t="s">
+        <v>186</v>
+      </c>
+      <c r="K174" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L174">
+        <v>456348</v>
+      </c>
+      <c r="N174" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456348</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175" s="6">
+        <v>9893790899</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="5">
+        <v>47678965569</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I175" t="s">
+        <v>187</v>
+      </c>
+      <c r="K175" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L175">
+        <v>456349</v>
+      </c>
+      <c r="N175" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456349</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" s="6">
+        <v>9893790900</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="5">
+        <v>47678965570</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I176" t="s">
+        <v>188</v>
+      </c>
+      <c r="K176" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L176">
+        <v>456350</v>
+      </c>
+      <c r="N176" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456350</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177" s="6">
+        <v>9893790901</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="5">
+        <v>47678965571</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I177" t="s">
+        <v>189</v>
+      </c>
+      <c r="K177" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L177">
+        <v>456351</v>
+      </c>
+      <c r="N177" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456351</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C178" s="6">
+        <v>9893790902</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="5">
+        <v>47678965572</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178" t="s">
+        <v>190</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L178">
+        <v>456352</v>
+      </c>
+      <c r="N178" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456352</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179" s="6">
+        <v>9893790903</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="5">
+        <v>47678965573</v>
+      </c>
+      <c r="G179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I179" t="s">
+        <v>191</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L179">
+        <v>456353</v>
+      </c>
+      <c r="N179" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456353</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180" s="6">
+        <v>9893790904</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="5">
+        <v>47678965574</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I180" t="s">
+        <v>192</v>
+      </c>
+      <c r="K180" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L180">
+        <v>456354</v>
+      </c>
+      <c r="N180" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456354</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181" s="6">
+        <v>9893790905</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="5">
+        <v>47678965575</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I181" t="s">
+        <v>193</v>
+      </c>
+      <c r="K181" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L181">
+        <v>456355</v>
+      </c>
+      <c r="N181" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456355</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C182" s="6">
+        <v>9893790906</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="5">
+        <v>47678965576</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H182" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I182" t="s">
+        <v>194</v>
+      </c>
+      <c r="K182" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L182">
+        <v>456356</v>
+      </c>
+      <c r="N182" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456356</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183" s="6">
+        <v>9893790907</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="5">
+        <v>47678965577</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H183" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I183" t="s">
+        <v>195</v>
+      </c>
+      <c r="K183" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L183">
+        <v>456357</v>
+      </c>
+      <c r="N183" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456357</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184" s="6">
+        <v>9893790908</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="5">
+        <v>47678965578</v>
+      </c>
+      <c r="G184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H184" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I184" t="s">
+        <v>196</v>
+      </c>
+      <c r="K184" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L184">
+        <v>456358</v>
+      </c>
+      <c r="N184" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456358</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C185" s="6">
+        <v>9893790909</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="5">
+        <v>47678965579</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I185" t="s">
+        <v>197</v>
+      </c>
+      <c r="K185" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L185">
+        <v>456359</v>
+      </c>
+      <c r="N185" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456359</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186" s="6">
+        <v>9893790910</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="5">
+        <v>47678965580</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I186" t="s">
+        <v>198</v>
+      </c>
+      <c r="K186" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L186">
+        <v>456360</v>
+      </c>
+      <c r="N186" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456360</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187" s="6">
+        <v>9893790911</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="5">
+        <v>47678965581</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I187" t="s">
+        <v>199</v>
+      </c>
+      <c r="K187" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L187">
+        <v>456361</v>
+      </c>
+      <c r="N187" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456361</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188" s="6">
+        <v>9893790912</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="5">
+        <v>47678965582</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H188" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I188" t="s">
+        <v>200</v>
+      </c>
+      <c r="K188" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L188">
+        <v>456362</v>
+      </c>
+      <c r="N188" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456362</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189" s="6">
+        <v>9893790913</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" s="5">
+        <v>47678965583</v>
+      </c>
+      <c r="G189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H189" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I189" t="s">
+        <v>201</v>
+      </c>
+      <c r="K189" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L189">
+        <v>456363</v>
+      </c>
+      <c r="N189" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456363</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" s="6">
+        <v>9893790914</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="5">
+        <v>47678965584</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H190" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I190" t="s">
+        <v>202</v>
+      </c>
+      <c r="K190" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L190">
+        <v>456364</v>
+      </c>
+      <c r="N190" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456364</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191" s="6">
+        <v>9893790915</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" s="5">
+        <v>47678965585</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H191" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I191" t="s">
+        <v>203</v>
+      </c>
+      <c r="K191" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L191">
+        <v>456365</v>
+      </c>
+      <c r="N191" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456365</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192" s="6">
+        <v>9893790916</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F192" s="5">
+        <v>47678965586</v>
+      </c>
+      <c r="G192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I192" t="s">
+        <v>204</v>
+      </c>
+      <c r="K192" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L192">
+        <v>456366</v>
+      </c>
+      <c r="N192" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456366</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C193" s="6">
+        <v>9893790917</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F193" s="5">
+        <v>47678965587</v>
+      </c>
+      <c r="G193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H193" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I193" t="s">
+        <v>205</v>
+      </c>
+      <c r="K193" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L193">
+        <v>456367</v>
+      </c>
+      <c r="N193" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456367</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194" s="6">
+        <v>9893790918</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F194" s="5">
+        <v>47678965588</v>
+      </c>
+      <c r="G194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H194" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I194" t="s">
+        <v>206</v>
+      </c>
+      <c r="K194" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L194">
+        <v>456368</v>
+      </c>
+      <c r="N194" t="str">
+        <f t="shared" si="2"/>
+        <v>GHE456368</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195" s="6">
+        <v>9893790919</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F195" s="5">
+        <v>47678965589</v>
+      </c>
+      <c r="G195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H195" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I195" t="s">
+        <v>207</v>
+      </c>
+      <c r="K195" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L195">
+        <v>456369</v>
+      </c>
+      <c r="N195" t="str">
+        <f t="shared" ref="N195:N206" si="3">K195&amp;L195</f>
+        <v>GHE456369</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C196" s="6">
+        <v>9893790920</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" s="5">
+        <v>47678965590</v>
+      </c>
+      <c r="G196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H196" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I196" t="s">
+        <v>208</v>
+      </c>
+      <c r="K196" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L196">
+        <v>456370</v>
+      </c>
+      <c r="N196" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456370</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" s="6">
+        <v>9893790921</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F197" s="5">
+        <v>47678965591</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H197" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I197" t="s">
+        <v>209</v>
+      </c>
+      <c r="K197" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L197">
+        <v>456371</v>
+      </c>
+      <c r="N197" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456371</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C198" s="6">
+        <v>9893790922</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F198" s="5">
+        <v>47678965592</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H198" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I198" t="s">
+        <v>210</v>
+      </c>
+      <c r="K198" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L198">
+        <v>456372</v>
+      </c>
+      <c r="N198" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456372</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C199" s="6">
+        <v>9893790923</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" s="5">
+        <v>47678965593</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H199" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I199" t="s">
+        <v>211</v>
+      </c>
+      <c r="K199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L199">
+        <v>456373</v>
+      </c>
+      <c r="N199" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456373</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200" s="6">
+        <v>9893790924</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" s="5">
+        <v>47678965594</v>
+      </c>
+      <c r="G200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H200" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I200" t="s">
+        <v>212</v>
+      </c>
+      <c r="K200" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L200">
+        <v>456374</v>
+      </c>
+      <c r="N200" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456374</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201" s="6">
+        <v>9893790925</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F201" s="5">
+        <v>47678965595</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H201" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I201" t="s">
+        <v>213</v>
+      </c>
+      <c r="K201" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L201">
+        <v>456375</v>
+      </c>
+      <c r="N201" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456375</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C202" s="6">
+        <v>9893790926</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F202" s="5">
+        <v>47678965596</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H202" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I202" t="s">
+        <v>214</v>
+      </c>
+      <c r="K202" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L202">
+        <v>456376</v>
+      </c>
+      <c r="N202" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456376</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A203" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203" s="6">
+        <v>9893790927</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F203" s="5">
+        <v>47678965597</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H203" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I203" t="s">
+        <v>215</v>
+      </c>
+      <c r="K203" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L203">
+        <v>456377</v>
+      </c>
+      <c r="N203" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456377</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204" s="6">
+        <v>9893790928</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F204" s="5">
+        <v>47678965598</v>
+      </c>
+      <c r="G204" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H204" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I204" t="s">
+        <v>216</v>
+      </c>
+      <c r="K204" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L204">
+        <v>456378</v>
+      </c>
+      <c r="N204" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456378</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205" s="6">
+        <v>9893790929</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F205" s="5">
+        <v>47678965599</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H205" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I205" t="s">
+        <v>217</v>
+      </c>
+      <c r="K205" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L205">
+        <v>456379</v>
+      </c>
+      <c r="N205" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456379</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" s="6">
+        <v>9893790930</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F206" s="5">
+        <v>47678965600</v>
+      </c>
+      <c r="G206" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H206" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I206" t="s">
+        <v>218</v>
+      </c>
+      <c r="K206" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L206">
+        <v>456380</v>
+      </c>
+      <c r="N206" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456380</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A207" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G207" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H207" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A208" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H208" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H209" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H210" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H211" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H212" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H213" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E214" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H214" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H215" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H216" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G217" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H217" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H218" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H219" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H220" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G222" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H222" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H224" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H225" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A226" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H226" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A227" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H227" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A228" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H228" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A229" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H229" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A230" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H230" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A231" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H231" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A232" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H232" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A233" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H233" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A234" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H234" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A235" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H235" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A236" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H236" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A237" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H237" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A238" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H238" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A239" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H239" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A240" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A241" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A242" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H242" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A243" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H243" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A244" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H244" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A245" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H245" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A246" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H246" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A247" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H247" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A248" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G248" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H248" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A249" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A250" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A251" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H251" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A252" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G252" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H252" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A253" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H253" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A254" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H254" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A255" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E255" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G255" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H255" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A256" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E256" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G256" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H256" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A257" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E257" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H257" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A258" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D258" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E258" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H258" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A259" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E259" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H259" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A260" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E260" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H260" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A261" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E261" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G261" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H261" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A262" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E262" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G262" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H262" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A263" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G263" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H263" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A264" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E264" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H264" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A265" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E265" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G265" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H265" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A266" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G266" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H266" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A267" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D267" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G267" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H267" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A268" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H268" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A269" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E269" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H269" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A270" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E270" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G270" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H270" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A271" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G271" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H271" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A272" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G272" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H272" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A273" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E273" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H273" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A274" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E274" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H274" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A275" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G275" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H275" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A276" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E276" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G276" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H276" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A277" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G277" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H277" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A278" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E278" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H278" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A279" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E279" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G279" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H279" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A280" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E280" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G280" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H280" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A281" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G281" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H281" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A282" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H282" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A283" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E283" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G283" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H283" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A284" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G284" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H284" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A285" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G285" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H285" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A286" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E286" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G286" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H286" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A287" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E287" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H287" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A288" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E288" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A289" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E289" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A290" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E290" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G290" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H290" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A291" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G291" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H291" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A292" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G292" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H292" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A293" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E293" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G293" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H293" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A294" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D294" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E294" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G294" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H294" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A295" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G295" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H295" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A296" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E296" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G296" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H296" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E297" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H297" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A298" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G298" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H298" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A299" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G299" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H299" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A300" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E300" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G300" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H300" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A301" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E301" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H301" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A302" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E302" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G302" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H302" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A303" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E303" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G303" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H303" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A304" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E304" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G304" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H304" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A305" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D305" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E305" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G305" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H305" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A306" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D306" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E306" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G306" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H306" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A307" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G307" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H307" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A308" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D308" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E308" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G308" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H308" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A309" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D309" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E309" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G309" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H309" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A310" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D310" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E310" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G310" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H310" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A311" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E311" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G311" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H311" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A312" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E312" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G312" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H312" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A313" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E313" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G313" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H313" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A314" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D314" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E314" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G314" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H314" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A315" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D315" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E315" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G315" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H315" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A316" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E316" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G316" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H316" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A317" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E317" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G317" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H317" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A318" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D318" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E318" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G318" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H318" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A319" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D319" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E319" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G319" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H319" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A320" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E320" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G320" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H320" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A321" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D321" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E321" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G321" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H321" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A322" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E322" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G322" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H322" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A323" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E323" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G323" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H323" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A324" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E324" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G324" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H324" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A325" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D325" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E325" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G325" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H325" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A326" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E326" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G326" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H326" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A327" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E327" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G327" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H327" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A328" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D328" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E328" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G328" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H328" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A329" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D329" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E329" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G329" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H329" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A330" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D330" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E330" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G330" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H330" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A331" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D331" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G331" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H331" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A332" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D332" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E332" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G332" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H332" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A333" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D333" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E333" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G333" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H333" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A334" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D334" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E334" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G334" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H334" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A335" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D335" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E335" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G335" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H335" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A336" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D336" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E336" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G336" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H336" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A337" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D337" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E337" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G337" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H337" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A338" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D338" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G338" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H338" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A339" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D339" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E339" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G339" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H339" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A340" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D340" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E340" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G340" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H340" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A341" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D341" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E341" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G341" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H341" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A342" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D342" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E342" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G342" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H342" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A343" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E343" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G343" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H343" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A344" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D344" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E344" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G344" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H344" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A345" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D345" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E345" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G345" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H345" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A346" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D346" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E346" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G346" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H346" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A347" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D347" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E347" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G347" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H347" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A348" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D348" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E348" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G348" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H348" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A349" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D349" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E349" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G349" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H349" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A350" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D350" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E350" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G350" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H350" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A351" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D351" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E351" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G351" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H351" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A352" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E352" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G352" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H352" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A353" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D353" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E353" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G353" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H353" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A354" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D354" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G354" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H354" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A355" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E355" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G355" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H355" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A356" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D356" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E356" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G356" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H356" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A357" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E357" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G357" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H357" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A358" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D358" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E358" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G358" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H358" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A359" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D359" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E359" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G359" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H359" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A360" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D360" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E360" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G360" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H360" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A361" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D361" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G361" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H361" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A362" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D362" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G362" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H362" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A363" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D363" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E363" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G363" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H363" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A364" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D364" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E364" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G364" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H364" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A365" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D365" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E365" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G365" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H365" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A366" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D366" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G366" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H366" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A367" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D367" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G367" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H367" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A368" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D368" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G368" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H368" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A369" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D369" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G369" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H369" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A370" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D370" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E370" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G370" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H370" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A371" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D371" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E371" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G371" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H371" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A372" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D372" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E372" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G372" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H372" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A373" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G373" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H373" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A374" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E374" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G374" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H374" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A375" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E375" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G375" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H375" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A376" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E376" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G376" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H376" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A377" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E377" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G377" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H377" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A378" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E378" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G378" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H378" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A379" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E379" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G379" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H379" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A380" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D380" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E380" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G380" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H380" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A381" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E381" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G381" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H381" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A382" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D382" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E382" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G382" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H382" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A383" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D383" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E383" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G383" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H383" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A384" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D384" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E384" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G384" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H384" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A385" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D385" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E385" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G385" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H385" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A386" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D386" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E386" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G386" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H386" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A387" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D387" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E387" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G387" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H387" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A388" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D388" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E388" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G388" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H388" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A389" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D389" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E389" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G389" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H389" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A390" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D390" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E390" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G390" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H390" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A391" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D391" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E391" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G391" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H391" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A392" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D392" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E392" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G392" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H392" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A393" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D393" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E393" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G393" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H393" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A394" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D394" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E394" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G394" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H394" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A395" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D395" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E395" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G395" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H395" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A396" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D396" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E396" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G396" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H396" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A397" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D397" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E397" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G397" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H397" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A398" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D398" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E398" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G398" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H398" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A399" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D399" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E399" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G399" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H399" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A400" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D400" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E400" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G400" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H400" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A401" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E401" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G401" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H401" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A402" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D402" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E402" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G402" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H402" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A403" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D403" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E403" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G403" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H403" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A404" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D404" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E404" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G404" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H404" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A405" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D405" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E405" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G405" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H405" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A406" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D406" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E406" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G406" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H406" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A407" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D407" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E407" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G407" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H407" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A408" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D408" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E408" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G408" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H408" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A409" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D409" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E409" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G409" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H409" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A410" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D410" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E410" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G410" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H410" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A411" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D411" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E411" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G411" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H411" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A412" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D412" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E412" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G412" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H412" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A413" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D413" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E413" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G413" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H413" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A414" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D414" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E414" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G414" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H414" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A415" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D415" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E415" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G415" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H415" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A416" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D416" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E416" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G416" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H416" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A417" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D417" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E417" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G417" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H417" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A418" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D418" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E418" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G418" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H418" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A419" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B419" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D419" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E419" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G419" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H419" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A420" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D420" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E420" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G420" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H420" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A421" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B421" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D421" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E421" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G421" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H421" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A422" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D422" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E422" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G422" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H422" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A423" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D423" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E423" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G423" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H423" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A424" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D424" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E424" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G424" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H424" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A425" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D425" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E425" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G425" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H425" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A426" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D426" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E426" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G426" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H426" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A427" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D427" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E427" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G427" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H427" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A428" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D428" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E428" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G428" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H428" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A429" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D429" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E429" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G429" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H429" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A430" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D430" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E430" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G430" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H430" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A431" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D431" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E431" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G431" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H431" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A432" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D432" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E432" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G432" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H432" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A433" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D433" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E433" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G433" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H433" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A434" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B434" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D434" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E434" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G434" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H434" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A435" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B435" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D435" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E435" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G435" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H435" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A436" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D436" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E436" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G436" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H436" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A437" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D437" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E437" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G437" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H437" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A438" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D438" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E438" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G438" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H438" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A439" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B439" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D439" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E439" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G439" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H439" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A440" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B440" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D440" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E440" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G440" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H440" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A441" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B441" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D441" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E441" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G441" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H441" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A442" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D442" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E442" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G442" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H442" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A443" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D443" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E443" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G443" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H443" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A444" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D444" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E444" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G444" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H444" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A445" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B445" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D445" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E445" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G445" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H445" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A446" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D446" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E446" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G446" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H446" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A447" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D447" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E447" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G447" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H447" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A448" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D448" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E448" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G448" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H448" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A449" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D449" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E449" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G449" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H449" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A450" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B450" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D450" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E450" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G450" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H450" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ID_Generators/POLAND_IDGenerator.xlsx
+++ b/Data/ID_Generators/POLAND_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\ID_Generators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5A8241-A676-4F19-95B9-652EB274964A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC69B4B8-EFAF-47A3-A4C4-6E5A19B3F178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="252">
   <si>
     <t>Country1</t>
   </si>
@@ -693,6 +693,105 @@
   </si>
   <si>
     <t>GHE456380</t>
+  </si>
+  <si>
+    <t>GHE456381</t>
+  </si>
+  <si>
+    <t>GHE456382</t>
+  </si>
+  <si>
+    <t>GHE456383</t>
+  </si>
+  <si>
+    <t>GHE456384</t>
+  </si>
+  <si>
+    <t>GHE456385</t>
+  </si>
+  <si>
+    <t>GHE456386</t>
+  </si>
+  <si>
+    <t>GHE456387</t>
+  </si>
+  <si>
+    <t>GHE456388</t>
+  </si>
+  <si>
+    <t>GHE456389</t>
+  </si>
+  <si>
+    <t>GHE456390</t>
+  </si>
+  <si>
+    <t>GHE456391</t>
+  </si>
+  <si>
+    <t>GHE456392</t>
+  </si>
+  <si>
+    <t>GHE456393</t>
+  </si>
+  <si>
+    <t>GHE456394</t>
+  </si>
+  <si>
+    <t>GHE456395</t>
+  </si>
+  <si>
+    <t>GHE456396</t>
+  </si>
+  <si>
+    <t>GHE456397</t>
+  </si>
+  <si>
+    <t>GHE456398</t>
+  </si>
+  <si>
+    <t>GHE456399</t>
+  </si>
+  <si>
+    <t>GHE456400</t>
+  </si>
+  <si>
+    <t>GHE456401</t>
+  </si>
+  <si>
+    <t>GHE456402</t>
+  </si>
+  <si>
+    <t>GHE456403</t>
+  </si>
+  <si>
+    <t>GHE456404</t>
+  </si>
+  <si>
+    <t>GHE456405</t>
+  </si>
+  <si>
+    <t>GHE456406</t>
+  </si>
+  <si>
+    <t>GHE456407</t>
+  </si>
+  <si>
+    <t>GHE456408</t>
+  </si>
+  <si>
+    <t>GHE456409</t>
+  </si>
+  <si>
+    <t>GHE456410</t>
+  </si>
+  <si>
+    <t>GHE456411</t>
+  </si>
+  <si>
+    <t>GHE456412</t>
+  </si>
+  <si>
+    <t>GHE456413</t>
   </si>
 </sst>
 </file>
@@ -8700,7 +8799,7 @@
         <v>456369</v>
       </c>
       <c r="N195" t="str">
-        <f t="shared" ref="N195:N206" si="3">K195&amp;L195</f>
+        <f t="shared" ref="N195:N239" si="3">K195&amp;L195</f>
         <v>GHE456369</v>
       </c>
     </row>
@@ -9140,17 +9239,36 @@
       <c r="B207" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C207" s="6">
+        <v>9893790931</v>
+      </c>
       <c r="D207" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E207" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F207" s="5">
+        <v>47678965601</v>
+      </c>
       <c r="G207" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H207" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I207" t="s">
+        <v>219</v>
+      </c>
+      <c r="K207" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L207">
+        <v>456381</v>
+      </c>
+      <c r="N207" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456381</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
@@ -9160,640 +9278,1248 @@
       <c r="B208" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C208" s="6">
+        <v>9893790932</v>
+      </c>
       <c r="D208" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E208" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F208" s="5">
+        <v>47678965602</v>
+      </c>
       <c r="G208" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H208" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I208" t="s">
+        <v>220</v>
+      </c>
+      <c r="K208" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L208">
+        <v>456382</v>
+      </c>
+      <c r="N208" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456382</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C209" s="6">
+        <v>9893790933</v>
+      </c>
       <c r="D209" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E209" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F209" s="5">
+        <v>47678965603</v>
+      </c>
       <c r="G209" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H209" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I209" t="s">
+        <v>221</v>
+      </c>
+      <c r="K209" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L209">
+        <v>456383</v>
+      </c>
+      <c r="N209" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456383</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C210" s="6">
+        <v>9893790934</v>
+      </c>
       <c r="D210" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E210" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F210" s="5">
+        <v>47678965604</v>
+      </c>
       <c r="G210" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H210" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I210" t="s">
+        <v>222</v>
+      </c>
+      <c r="K210" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L210">
+        <v>456384</v>
+      </c>
+      <c r="N210" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456384</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C211" s="6">
+        <v>9893790935</v>
+      </c>
       <c r="D211" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E211" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F211" s="5">
+        <v>47678965605</v>
+      </c>
       <c r="G211" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H211" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I211" t="s">
+        <v>223</v>
+      </c>
+      <c r="K211" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L211">
+        <v>456385</v>
+      </c>
+      <c r="N211" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456385</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C212" s="6">
+        <v>9893790936</v>
+      </c>
       <c r="D212" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E212" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F212" s="5">
+        <v>47678965606</v>
+      </c>
       <c r="G212" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H212" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I212" t="s">
+        <v>224</v>
+      </c>
+      <c r="K212" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L212">
+        <v>456386</v>
+      </c>
+      <c r="N212" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456386</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C213" s="6">
+        <v>9893790937</v>
+      </c>
       <c r="D213" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E213" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F213" s="5">
+        <v>47678965607</v>
+      </c>
       <c r="G213" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H213" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I213" t="s">
+        <v>225</v>
+      </c>
+      <c r="K213" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L213">
+        <v>456387</v>
+      </c>
+      <c r="N213" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456387</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C214" s="6">
+        <v>9893790938</v>
+      </c>
       <c r="D214" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E214" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F214" s="5">
+        <v>47678965608</v>
+      </c>
       <c r="G214" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H214" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I214" t="s">
+        <v>226</v>
+      </c>
+      <c r="K214" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L214">
+        <v>456388</v>
+      </c>
+      <c r="N214" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456388</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C215" s="6">
+        <v>9893790939</v>
+      </c>
       <c r="D215" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E215" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F215" s="5">
+        <v>47678965609</v>
+      </c>
       <c r="G215" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H215" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I215" t="s">
+        <v>227</v>
+      </c>
+      <c r="K215" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L215">
+        <v>456389</v>
+      </c>
+      <c r="N215" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456389</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C216" s="6">
+        <v>9893790940</v>
+      </c>
       <c r="D216" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E216" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F216" s="5">
+        <v>47678965610</v>
+      </c>
       <c r="G216" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H216" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I216" t="s">
+        <v>228</v>
+      </c>
+      <c r="K216" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L216">
+        <v>456390</v>
+      </c>
+      <c r="N216" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456390</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C217" s="6">
+        <v>9893790941</v>
+      </c>
       <c r="D217" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F217" s="5">
+        <v>47678965611</v>
+      </c>
       <c r="G217" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H217" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I217" t="s">
+        <v>229</v>
+      </c>
+      <c r="K217" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L217">
+        <v>456391</v>
+      </c>
+      <c r="N217" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456391</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C218" s="6">
+        <v>9893790942</v>
+      </c>
       <c r="D218" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E218" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F218" s="5">
+        <v>47678965612</v>
+      </c>
       <c r="G218" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H218" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I218" t="s">
+        <v>230</v>
+      </c>
+      <c r="K218" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L218">
+        <v>456392</v>
+      </c>
+      <c r="N218" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456392</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C219" s="6">
+        <v>9893790943</v>
+      </c>
       <c r="D219" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F219" s="5">
+        <v>47678965613</v>
+      </c>
       <c r="G219" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H219" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I219" t="s">
+        <v>231</v>
+      </c>
+      <c r="K219" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L219">
+        <v>456393</v>
+      </c>
+      <c r="N219" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456393</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C220" s="6">
+        <v>9893790944</v>
+      </c>
       <c r="D220" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E220" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F220" s="5">
+        <v>47678965614</v>
+      </c>
       <c r="G220" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H220" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I220" t="s">
+        <v>232</v>
+      </c>
+      <c r="K220" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L220">
+        <v>456394</v>
+      </c>
+      <c r="N220" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456394</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C221" s="6">
+        <v>9893790945</v>
+      </c>
       <c r="D221" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F221" s="5">
+        <v>47678965615</v>
+      </c>
       <c r="G221" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H221" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I221" t="s">
+        <v>233</v>
+      </c>
+      <c r="K221" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L221">
+        <v>456395</v>
+      </c>
+      <c r="N221" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456395</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C222" s="6">
+        <v>9893790946</v>
+      </c>
       <c r="D222" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E222" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F222" s="5">
+        <v>47678965616</v>
+      </c>
       <c r="G222" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H222" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I222" t="s">
+        <v>234</v>
+      </c>
+      <c r="K222" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L222">
+        <v>456396</v>
+      </c>
+      <c r="N222" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456396</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C223" s="6">
+        <v>9893790947</v>
+      </c>
       <c r="D223" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E223" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F223" s="5">
+        <v>47678965617</v>
+      </c>
       <c r="G223" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H223" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I223" t="s">
+        <v>235</v>
+      </c>
+      <c r="K223" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L223">
+        <v>456397</v>
+      </c>
+      <c r="N223" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456397</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C224" s="6">
+        <v>9893790948</v>
+      </c>
       <c r="D224" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E224" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F224" s="5">
+        <v>47678965618</v>
+      </c>
       <c r="G224" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H224" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I224" t="s">
+        <v>236</v>
+      </c>
+      <c r="K224" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L224">
+        <v>456398</v>
+      </c>
+      <c r="N224" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456398</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C225" s="6">
+        <v>9893790949</v>
+      </c>
       <c r="D225" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E225" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F225" s="5">
+        <v>47678965619</v>
+      </c>
       <c r="G225" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H225" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I225" t="s">
+        <v>237</v>
+      </c>
+      <c r="K225" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L225">
+        <v>456399</v>
+      </c>
+      <c r="N225" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456399</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C226" s="6">
+        <v>9893790950</v>
+      </c>
       <c r="D226" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E226" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F226" s="5">
+        <v>47678965620</v>
+      </c>
       <c r="G226" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H226" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I226" t="s">
+        <v>238</v>
+      </c>
+      <c r="K226" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L226">
+        <v>456400</v>
+      </c>
+      <c r="N226" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456400</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C227" s="6">
+        <v>9893790951</v>
+      </c>
       <c r="D227" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E227" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F227" s="5">
+        <v>47678965621</v>
+      </c>
       <c r="G227" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H227" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I227" t="s">
+        <v>239</v>
+      </c>
+      <c r="K227" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L227">
+        <v>456401</v>
+      </c>
+      <c r="N227" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456401</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C228" s="6">
+        <v>9893790952</v>
+      </c>
       <c r="D228" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E228" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F228" s="5">
+        <v>47678965622</v>
+      </c>
       <c r="G228" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H228" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I228" t="s">
+        <v>240</v>
+      </c>
+      <c r="K228" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L228">
+        <v>456402</v>
+      </c>
+      <c r="N228" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456402</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C229" s="6">
+        <v>9893790953</v>
+      </c>
       <c r="D229" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E229" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F229" s="5">
+        <v>47678965623</v>
+      </c>
       <c r="G229" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H229" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I229" t="s">
+        <v>241</v>
+      </c>
+      <c r="K229" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L229">
+        <v>456403</v>
+      </c>
+      <c r="N229" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456403</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C230" s="6">
+        <v>9893790954</v>
+      </c>
       <c r="D230" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F230" s="5">
+        <v>47678965624</v>
+      </c>
       <c r="G230" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H230" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I230" t="s">
+        <v>242</v>
+      </c>
+      <c r="K230" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L230">
+        <v>456404</v>
+      </c>
+      <c r="N230" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456404</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C231" s="6">
+        <v>9893790955</v>
+      </c>
       <c r="D231" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E231" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F231" s="5">
+        <v>47678965625</v>
+      </c>
       <c r="G231" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H231" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I231" t="s">
+        <v>243</v>
+      </c>
+      <c r="K231" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L231">
+        <v>456405</v>
+      </c>
+      <c r="N231" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456405</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C232" s="6">
+        <v>9893790956</v>
+      </c>
       <c r="D232" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E232" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F232" s="5">
+        <v>47678965626</v>
+      </c>
       <c r="G232" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H232" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I232" t="s">
+        <v>244</v>
+      </c>
+      <c r="K232" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L232">
+        <v>456406</v>
+      </c>
+      <c r="N232" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456406</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C233" s="6">
+        <v>9893790957</v>
+      </c>
       <c r="D233" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E233" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F233" s="5">
+        <v>47678965627</v>
+      </c>
       <c r="G233" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H233" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I233" t="s">
+        <v>245</v>
+      </c>
+      <c r="K233" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L233">
+        <v>456407</v>
+      </c>
+      <c r="N233" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456407</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C234" s="6">
+        <v>9893790958</v>
+      </c>
       <c r="D234" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E234" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F234" s="5">
+        <v>47678965628</v>
+      </c>
       <c r="G234" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H234" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I234" t="s">
+        <v>246</v>
+      </c>
+      <c r="K234" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L234">
+        <v>456408</v>
+      </c>
+      <c r="N234" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456408</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C235" s="6">
+        <v>9893790959</v>
+      </c>
       <c r="D235" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F235" s="5">
+        <v>47678965629</v>
+      </c>
       <c r="G235" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H235" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I235" t="s">
+        <v>247</v>
+      </c>
+      <c r="K235" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L235">
+        <v>456409</v>
+      </c>
+      <c r="N235" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456409</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C236" s="6">
+        <v>9893790960</v>
+      </c>
       <c r="D236" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E236" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F236" s="5">
+        <v>47678965630</v>
+      </c>
       <c r="G236" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H236" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I236" t="s">
+        <v>248</v>
+      </c>
+      <c r="K236" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L236">
+        <v>456410</v>
+      </c>
+      <c r="N236" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456410</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C237" s="6">
+        <v>9893790961</v>
+      </c>
       <c r="D237" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E237" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F237" s="5">
+        <v>47678965631</v>
+      </c>
       <c r="G237" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H237" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I237" t="s">
+        <v>249</v>
+      </c>
+      <c r="K237" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L237">
+        <v>456411</v>
+      </c>
+      <c r="N237" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456411</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C238" s="6">
+        <v>9893790962</v>
+      </c>
       <c r="D238" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E238" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F238" s="5">
+        <v>47678965632</v>
+      </c>
       <c r="G238" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H238" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I238" t="s">
+        <v>250</v>
+      </c>
+      <c r="K238" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L238">
+        <v>456412</v>
+      </c>
+      <c r="N238" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456412</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C239" s="6">
+        <v>9893790963</v>
+      </c>
       <c r="D239" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E239" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F239" s="5">
+        <v>47678965633</v>
+      </c>
       <c r="G239" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H239" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I239" t="s">
+        <v>251</v>
+      </c>
+      <c r="K239" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L239">
+        <v>456413</v>
+      </c>
+      <c r="N239" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456413</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="5" t="s">
         <v>9</v>
       </c>

--- a/Data/ID_Generators/POLAND_IDGenerator.xlsx
+++ b/Data/ID_Generators/POLAND_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\ID_Generators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC69B4B8-EFAF-47A3-A4C4-6E5A19B3F178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C551F0B-835F-4725-B692-DA4452D99B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="289">
   <si>
     <t>Country1</t>
   </si>
@@ -792,6 +792,117 @@
   </si>
   <si>
     <t>GHE456413</t>
+  </si>
+  <si>
+    <t>GHE456414</t>
+  </si>
+  <si>
+    <t>GHE456415</t>
+  </si>
+  <si>
+    <t>GHE456416</t>
+  </si>
+  <si>
+    <t>GHE456417</t>
+  </si>
+  <si>
+    <t>GHE456418</t>
+  </si>
+  <si>
+    <t>GHE456419</t>
+  </si>
+  <si>
+    <t>GHE456420</t>
+  </si>
+  <si>
+    <t>GHE456421</t>
+  </si>
+  <si>
+    <t>GHE456422</t>
+  </si>
+  <si>
+    <t>GHE456423</t>
+  </si>
+  <si>
+    <t>GHE456424</t>
+  </si>
+  <si>
+    <t>GHE456425</t>
+  </si>
+  <si>
+    <t>GHE456426</t>
+  </si>
+  <si>
+    <t>GHE456427</t>
+  </si>
+  <si>
+    <t>GHE456428</t>
+  </si>
+  <si>
+    <t>GHE456429</t>
+  </si>
+  <si>
+    <t>GHE456430</t>
+  </si>
+  <si>
+    <t>GHE456431</t>
+  </si>
+  <si>
+    <t>GHE456432</t>
+  </si>
+  <si>
+    <t>GHE456433</t>
+  </si>
+  <si>
+    <t>GHE456434</t>
+  </si>
+  <si>
+    <t>GHE456435</t>
+  </si>
+  <si>
+    <t>GHE456436</t>
+  </si>
+  <si>
+    <t>GHE456437</t>
+  </si>
+  <si>
+    <t>GHE456438</t>
+  </si>
+  <si>
+    <t>GHE456439</t>
+  </si>
+  <si>
+    <t>GHE456440</t>
+  </si>
+  <si>
+    <t>GHE456441</t>
+  </si>
+  <si>
+    <t>GHE456442</t>
+  </si>
+  <si>
+    <t>GHE456443</t>
+  </si>
+  <si>
+    <t>GHE456444</t>
+  </si>
+  <si>
+    <t>GHE456445</t>
+  </si>
+  <si>
+    <t>GHE456446</t>
+  </si>
+  <si>
+    <t>GHE456447</t>
+  </si>
+  <si>
+    <t>GHE456448</t>
+  </si>
+  <si>
+    <t>GHE456449</t>
+  </si>
+  <si>
+    <t>GHE456450</t>
   </si>
 </sst>
 </file>
@@ -8799,7 +8910,7 @@
         <v>456369</v>
       </c>
       <c r="N195" t="str">
-        <f t="shared" ref="N195:N239" si="3">K195&amp;L195</f>
+        <f t="shared" ref="N195:N260" si="3">K195&amp;L195</f>
         <v>GHE456369</v>
       </c>
     </row>
@@ -10526,740 +10637,1443 @@
       <c r="B240" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C240" s="6">
+        <v>9893790964</v>
+      </c>
       <c r="D240" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E240" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F240" s="5">
+        <v>47678965634</v>
+      </c>
       <c r="G240" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I240" t="s">
+        <v>252</v>
+      </c>
+      <c r="K240" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L240">
+        <v>456414</v>
+      </c>
+      <c r="N240" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456414</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C241" s="6">
+        <v>9893790965</v>
+      </c>
       <c r="D241" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E241" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F241" s="5">
+        <v>47678965635</v>
+      </c>
       <c r="G241" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I241" t="s">
+        <v>253</v>
+      </c>
+      <c r="K241" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L241">
+        <v>456415</v>
+      </c>
+      <c r="N241" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456415</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C242" s="6">
+        <v>9893790966</v>
+      </c>
       <c r="D242" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F242" s="5">
+        <v>47678965636</v>
+      </c>
       <c r="G242" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I242" t="s">
+        <v>254</v>
+      </c>
+      <c r="K242" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L242">
+        <v>456416</v>
+      </c>
+      <c r="N242" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456416</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C243" s="6">
+        <v>9893790967</v>
+      </c>
       <c r="D243" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F243" s="5">
+        <v>47678965637</v>
+      </c>
       <c r="G243" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I243" t="s">
+        <v>255</v>
+      </c>
+      <c r="K243" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L243">
+        <v>456417</v>
+      </c>
+      <c r="N243" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456417</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C244" s="6">
+        <v>9893790968</v>
+      </c>
       <c r="D244" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E244" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F244" s="5">
+        <v>47678965638</v>
+      </c>
       <c r="G244" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I244" t="s">
+        <v>256</v>
+      </c>
+      <c r="K244" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L244">
+        <v>456418</v>
+      </c>
+      <c r="N244" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456418</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C245" s="6">
+        <v>9893790969</v>
+      </c>
       <c r="D245" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E245" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F245" s="5">
+        <v>47678965639</v>
+      </c>
       <c r="G245" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I245" t="s">
+        <v>257</v>
+      </c>
+      <c r="K245" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L245">
+        <v>456419</v>
+      </c>
+      <c r="N245" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456419</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C246" s="6">
+        <v>9893790970</v>
+      </c>
       <c r="D246" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E246" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F246" s="5">
+        <v>47678965640</v>
+      </c>
       <c r="G246" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I246" t="s">
+        <v>258</v>
+      </c>
+      <c r="K246" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L246">
+        <v>456420</v>
+      </c>
+      <c r="N246" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456420</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C247" s="6">
+        <v>9893790971</v>
+      </c>
       <c r="D247" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E247" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F247" s="5">
+        <v>47678965641</v>
+      </c>
       <c r="G247" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I247" t="s">
+        <v>259</v>
+      </c>
+      <c r="K247" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L247">
+        <v>456421</v>
+      </c>
+      <c r="N247" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456421</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C248" s="6">
+        <v>9893790972</v>
+      </c>
       <c r="D248" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E248" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F248" s="5">
+        <v>47678965642</v>
+      </c>
       <c r="G248" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I248" t="s">
+        <v>260</v>
+      </c>
+      <c r="K248" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L248">
+        <v>456422</v>
+      </c>
+      <c r="N248" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456422</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C249" s="6">
+        <v>9893790973</v>
+      </c>
       <c r="D249" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E249" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F249" s="5">
+        <v>47678965643</v>
+      </c>
       <c r="G249" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I249" t="s">
+        <v>261</v>
+      </c>
+      <c r="K249" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L249">
+        <v>456423</v>
+      </c>
+      <c r="N249" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456423</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C250" s="6">
+        <v>9893790974</v>
+      </c>
       <c r="D250" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E250" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F250" s="5">
+        <v>47678965644</v>
+      </c>
       <c r="G250" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I250" t="s">
+        <v>262</v>
+      </c>
+      <c r="K250" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L250">
+        <v>456424</v>
+      </c>
+      <c r="N250" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456424</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C251" s="6">
+        <v>9893790975</v>
+      </c>
       <c r="D251" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E251" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F251" s="5">
+        <v>47678965645</v>
+      </c>
       <c r="G251" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I251" t="s">
+        <v>263</v>
+      </c>
+      <c r="K251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L251">
+        <v>456425</v>
+      </c>
+      <c r="N251" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456425</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C252" s="6">
+        <v>9893790976</v>
+      </c>
       <c r="D252" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E252" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F252" s="5">
+        <v>47678965646</v>
+      </c>
       <c r="G252" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H252" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I252" t="s">
+        <v>264</v>
+      </c>
+      <c r="K252" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L252">
+        <v>456426</v>
+      </c>
+      <c r="N252" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456426</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C253" s="6">
+        <v>9893790977</v>
+      </c>
       <c r="D253" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E253" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F253" s="5">
+        <v>47678965647</v>
+      </c>
       <c r="G253" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H253" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I253" t="s">
+        <v>265</v>
+      </c>
+      <c r="K253" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L253">
+        <v>456427</v>
+      </c>
+      <c r="N253" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456427</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C254" s="6">
+        <v>9893790978</v>
+      </c>
       <c r="D254" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E254" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F254" s="5">
+        <v>47678965648</v>
+      </c>
       <c r="G254" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H254" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I254" t="s">
+        <v>266</v>
+      </c>
+      <c r="K254" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L254">
+        <v>456428</v>
+      </c>
+      <c r="N254" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456428</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C255" s="6">
+        <v>9893790979</v>
+      </c>
       <c r="D255" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E255" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F255" s="5">
+        <v>47678965649</v>
+      </c>
       <c r="G255" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H255" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I255" t="s">
+        <v>267</v>
+      </c>
+      <c r="K255" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L255">
+        <v>456429</v>
+      </c>
+      <c r="N255" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456429</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C256" s="6">
+        <v>9893790980</v>
+      </c>
       <c r="D256" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E256" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F256" s="5">
+        <v>47678965650</v>
+      </c>
       <c r="G256" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I256" t="s">
+        <v>268</v>
+      </c>
+      <c r="K256" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L256">
+        <v>456430</v>
+      </c>
+      <c r="N256" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456430</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C257" s="6">
+        <v>9893790981</v>
+      </c>
       <c r="D257" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E257" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F257" s="5">
+        <v>47678965651</v>
+      </c>
       <c r="G257" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H257" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I257" t="s">
+        <v>269</v>
+      </c>
+      <c r="K257" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L257">
+        <v>456431</v>
+      </c>
+      <c r="N257" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456431</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C258" s="6">
+        <v>9893790982</v>
+      </c>
       <c r="D258" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E258" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F258" s="5">
+        <v>47678965652</v>
+      </c>
       <c r="G258" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I258" t="s">
+        <v>270</v>
+      </c>
+      <c r="K258" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L258">
+        <v>456432</v>
+      </c>
+      <c r="N258" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456432</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C259" s="6">
+        <v>9893790983</v>
+      </c>
       <c r="D259" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F259" s="5">
+        <v>47678965653</v>
+      </c>
       <c r="G259" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H259" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I259" t="s">
+        <v>271</v>
+      </c>
+      <c r="K259" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L259">
+        <v>456433</v>
+      </c>
+      <c r="N259" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456433</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C260" s="6">
+        <v>9893790984</v>
+      </c>
       <c r="D260" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F260" s="5">
+        <v>47678965654</v>
+      </c>
       <c r="G260" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H260" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I260" t="s">
+        <v>272</v>
+      </c>
+      <c r="K260" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L260">
+        <v>456434</v>
+      </c>
+      <c r="N260" t="str">
+        <f t="shared" si="3"/>
+        <v>GHE456434</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C261" s="6">
+        <v>9893790985</v>
+      </c>
       <c r="D261" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F261" s="5">
+        <v>47678965655</v>
+      </c>
       <c r="G261" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H261" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I261" t="s">
+        <v>273</v>
+      </c>
+      <c r="K261" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L261">
+        <v>456435</v>
+      </c>
+      <c r="N261" t="str">
+        <f t="shared" ref="N261:N276" si="4">K261&amp;L261</f>
+        <v>GHE456435</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C262" s="6">
+        <v>9893790986</v>
+      </c>
       <c r="D262" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F262" s="5">
+        <v>47678965656</v>
+      </c>
       <c r="G262" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H262" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I262" t="s">
+        <v>274</v>
+      </c>
+      <c r="K262" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L262">
+        <v>456436</v>
+      </c>
+      <c r="N262" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456436</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C263" s="6">
+        <v>9893790987</v>
+      </c>
       <c r="D263" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E263" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F263" s="5">
+        <v>47678965657</v>
+      </c>
       <c r="G263" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H263" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I263" t="s">
+        <v>275</v>
+      </c>
+      <c r="K263" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L263">
+        <v>456437</v>
+      </c>
+      <c r="N263" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456437</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C264" s="6">
+        <v>9893790988</v>
+      </c>
       <c r="D264" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F264" s="5">
+        <v>47678965658</v>
+      </c>
       <c r="G264" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H264" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I264" t="s">
+        <v>276</v>
+      </c>
+      <c r="K264" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L264">
+        <v>456438</v>
+      </c>
+      <c r="N264" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456438</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C265" s="6">
+        <v>9893790989</v>
+      </c>
       <c r="D265" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E265" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F265" s="5">
+        <v>47678965659</v>
+      </c>
       <c r="G265" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H265" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I265" t="s">
+        <v>277</v>
+      </c>
+      <c r="K265" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L265">
+        <v>456439</v>
+      </c>
+      <c r="N265" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456439</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C266" s="6">
+        <v>9893790990</v>
+      </c>
       <c r="D266" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F266" s="5">
+        <v>47678965660</v>
+      </c>
       <c r="G266" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H266" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I266" t="s">
+        <v>278</v>
+      </c>
+      <c r="K266" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L266">
+        <v>456440</v>
+      </c>
+      <c r="N266" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456440</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C267" s="6">
+        <v>9893790991</v>
+      </c>
       <c r="D267" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E267" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F267" s="5">
+        <v>47678965661</v>
+      </c>
       <c r="G267" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H267" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K267" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L267">
+        <v>456441</v>
+      </c>
+      <c r="N267" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456441</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C268" s="6">
+        <v>9893790992</v>
+      </c>
       <c r="D268" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E268" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F268" s="5">
+        <v>47678965662</v>
+      </c>
       <c r="G268" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I268" t="s">
+        <v>280</v>
+      </c>
+      <c r="K268" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L268">
+        <v>456442</v>
+      </c>
+      <c r="N268" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456442</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C269" s="6">
+        <v>9893790993</v>
+      </c>
       <c r="D269" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E269" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F269" s="5">
+        <v>47678965663</v>
+      </c>
       <c r="G269" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I269" t="s">
+        <v>281</v>
+      </c>
+      <c r="K269" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L269">
+        <v>456443</v>
+      </c>
+      <c r="N269" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456443</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C270" s="6">
+        <v>9893790994</v>
+      </c>
       <c r="D270" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E270" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F270" s="5">
+        <v>47678965664</v>
+      </c>
       <c r="G270" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I270" t="s">
+        <v>282</v>
+      </c>
+      <c r="K270" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L270">
+        <v>456444</v>
+      </c>
+      <c r="N270" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456444</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C271" s="6">
+        <v>9893790995</v>
+      </c>
       <c r="D271" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E271" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F271" s="5">
+        <v>47678965665</v>
+      </c>
       <c r="G271" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I271" t="s">
+        <v>283</v>
+      </c>
+      <c r="K271" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L271">
+        <v>456445</v>
+      </c>
+      <c r="N271" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456445</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B272" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C272" s="6">
+        <v>9893790996</v>
+      </c>
       <c r="D272" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E272" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F272" s="5">
+        <v>47678965666</v>
+      </c>
       <c r="G272" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I272" t="s">
+        <v>284</v>
+      </c>
+      <c r="K272" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L272">
+        <v>456446</v>
+      </c>
+      <c r="N272" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456446</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C273" s="6">
+        <v>9893790997</v>
+      </c>
       <c r="D273" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E273" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F273" s="5">
+        <v>47678965667</v>
+      </c>
       <c r="G273" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I273" t="s">
+        <v>285</v>
+      </c>
+      <c r="K273" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L273">
+        <v>456447</v>
+      </c>
+      <c r="N273" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456447</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B274" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C274" s="6">
+        <v>9893790998</v>
+      </c>
       <c r="D274" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E274" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F274" s="5">
+        <v>47678965668</v>
+      </c>
       <c r="G274" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I274" t="s">
+        <v>286</v>
+      </c>
+      <c r="K274" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L274">
+        <v>456448</v>
+      </c>
+      <c r="N274" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456448</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C275" s="6">
+        <v>9893790999</v>
+      </c>
       <c r="D275" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F275" s="5">
+        <v>47678965669</v>
+      </c>
       <c r="G275" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I275" t="s">
+        <v>287</v>
+      </c>
+      <c r="K275" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L275">
+        <v>456449</v>
+      </c>
+      <c r="N275" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456449</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B276" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C276" s="6">
+        <v>9893791000</v>
+      </c>
       <c r="D276" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E276" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F276" s="5">
+        <v>47678965670</v>
+      </c>
       <c r="G276" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H276" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I276" t="s">
+        <v>288</v>
+      </c>
+      <c r="K276" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L276">
+        <v>456450</v>
+      </c>
+      <c r="N276" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456450</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="5" t="s">
         <v>9</v>
       </c>
@@ -11279,7 +12093,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="5" t="s">
         <v>9</v>
       </c>
@@ -11299,7 +12113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="5" t="s">
         <v>9</v>
       </c>
@@ -11319,7 +12133,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="5" t="s">
         <v>9</v>
       </c>
@@ -11339,7 +12153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="5" t="s">
         <v>9</v>
       </c>
@@ -11359,7 +12173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="5" t="s">
         <v>9</v>
       </c>
@@ -11379,7 +12193,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="5" t="s">
         <v>9</v>
       </c>
@@ -11399,7 +12213,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="5" t="s">
         <v>9</v>
       </c>
@@ -11419,7 +12233,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="5" t="s">
         <v>9</v>
       </c>
@@ -11439,7 +12253,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="5" t="s">
         <v>9</v>
       </c>
@@ -11459,7 +12273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="5" t="s">
         <v>9</v>
       </c>
@@ -11479,7 +12293,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="5" t="s">
         <v>9</v>
       </c>

--- a/Data/ID_Generators/POLAND_IDGenerator.xlsx
+++ b/Data/ID_Generators/POLAND_IDGenerator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WorkdayPlaywright\Data\ID_Generators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C551F0B-835F-4725-B692-DA4452D99B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911D15E7-749A-42C5-BED2-DE5B7EB71D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3689" uniqueCount="474">
   <si>
     <t>Country1</t>
   </si>
@@ -903,6 +903,561 @@
   </si>
   <si>
     <t>GHE456450</t>
+  </si>
+  <si>
+    <t>GHE456451</t>
+  </si>
+  <si>
+    <t>GHE456452</t>
+  </si>
+  <si>
+    <t>GHE456453</t>
+  </si>
+  <si>
+    <t>GHE456454</t>
+  </si>
+  <si>
+    <t>GHE456455</t>
+  </si>
+  <si>
+    <t>GHE456456</t>
+  </si>
+  <si>
+    <t>GHE456457</t>
+  </si>
+  <si>
+    <t>GHE456458</t>
+  </si>
+  <si>
+    <t>GHE456459</t>
+  </si>
+  <si>
+    <t>GHE456460</t>
+  </si>
+  <si>
+    <t>GHE456461</t>
+  </si>
+  <si>
+    <t>GHE456462</t>
+  </si>
+  <si>
+    <t>GHE456463</t>
+  </si>
+  <si>
+    <t>GHE456464</t>
+  </si>
+  <si>
+    <t>GHE456465</t>
+  </si>
+  <si>
+    <t>GHE456466</t>
+  </si>
+  <si>
+    <t>GHE456467</t>
+  </si>
+  <si>
+    <t>GHE456468</t>
+  </si>
+  <si>
+    <t>GHE456469</t>
+  </si>
+  <si>
+    <t>GHE456470</t>
+  </si>
+  <si>
+    <t>GHE456471</t>
+  </si>
+  <si>
+    <t>GHE456472</t>
+  </si>
+  <si>
+    <t>GHE456473</t>
+  </si>
+  <si>
+    <t>GHE456474</t>
+  </si>
+  <si>
+    <t>GHE456475</t>
+  </si>
+  <si>
+    <t>GHE456476</t>
+  </si>
+  <si>
+    <t>GHE456477</t>
+  </si>
+  <si>
+    <t>GHE456478</t>
+  </si>
+  <si>
+    <t>GHE456479</t>
+  </si>
+  <si>
+    <t>GHE456480</t>
+  </si>
+  <si>
+    <t>GHE456481</t>
+  </si>
+  <si>
+    <t>GHE456482</t>
+  </si>
+  <si>
+    <t>GHE456483</t>
+  </si>
+  <si>
+    <t>GHE456484</t>
+  </si>
+  <si>
+    <t>GHE456485</t>
+  </si>
+  <si>
+    <t>GHE456486</t>
+  </si>
+  <si>
+    <t>GHE456487</t>
+  </si>
+  <si>
+    <t>GHE456488</t>
+  </si>
+  <si>
+    <t>GHE456489</t>
+  </si>
+  <si>
+    <t>GHE456490</t>
+  </si>
+  <si>
+    <t>GHE456491</t>
+  </si>
+  <si>
+    <t>GHE456492</t>
+  </si>
+  <si>
+    <t>GHE456493</t>
+  </si>
+  <si>
+    <t>GHE456494</t>
+  </si>
+  <si>
+    <t>GHE456495</t>
+  </si>
+  <si>
+    <t>GHE456496</t>
+  </si>
+  <si>
+    <t>GHE456497</t>
+  </si>
+  <si>
+    <t>GHE456498</t>
+  </si>
+  <si>
+    <t>GHE456499</t>
+  </si>
+  <si>
+    <t>GHE456500</t>
+  </si>
+  <si>
+    <t>GHE456501</t>
+  </si>
+  <si>
+    <t>GHE456502</t>
+  </si>
+  <si>
+    <t>GHE456503</t>
+  </si>
+  <si>
+    <t>GHE456504</t>
+  </si>
+  <si>
+    <t>GHE456505</t>
+  </si>
+  <si>
+    <t>GHE456506</t>
+  </si>
+  <si>
+    <t>GHE456507</t>
+  </si>
+  <si>
+    <t>GHE456508</t>
+  </si>
+  <si>
+    <t>GHE456509</t>
+  </si>
+  <si>
+    <t>GHE456510</t>
+  </si>
+  <si>
+    <t>GHE456511</t>
+  </si>
+  <si>
+    <t>GHE456512</t>
+  </si>
+  <si>
+    <t>GHE456513</t>
+  </si>
+  <si>
+    <t>GHE456514</t>
+  </si>
+  <si>
+    <t>GHE456515</t>
+  </si>
+  <si>
+    <t>GHE456516</t>
+  </si>
+  <si>
+    <t>GHE456517</t>
+  </si>
+  <si>
+    <t>GHE456518</t>
+  </si>
+  <si>
+    <t>GHE456519</t>
+  </si>
+  <si>
+    <t>GHE456520</t>
+  </si>
+  <si>
+    <t>GHE456521</t>
+  </si>
+  <si>
+    <t>GHE456522</t>
+  </si>
+  <si>
+    <t>GHE456523</t>
+  </si>
+  <si>
+    <t>GHE456524</t>
+  </si>
+  <si>
+    <t>GHE456525</t>
+  </si>
+  <si>
+    <t>GHE456526</t>
+  </si>
+  <si>
+    <t>GHE456527</t>
+  </si>
+  <si>
+    <t>GHE456528</t>
+  </si>
+  <si>
+    <t>GHE456529</t>
+  </si>
+  <si>
+    <t>GHE456530</t>
+  </si>
+  <si>
+    <t>GHE456531</t>
+  </si>
+  <si>
+    <t>GHE456532</t>
+  </si>
+  <si>
+    <t>GHE456533</t>
+  </si>
+  <si>
+    <t>GHE456534</t>
+  </si>
+  <si>
+    <t>GHE456535</t>
+  </si>
+  <si>
+    <t>GHE456536</t>
+  </si>
+  <si>
+    <t>GHE456537</t>
+  </si>
+  <si>
+    <t>GHE456538</t>
+  </si>
+  <si>
+    <t>GHE456539</t>
+  </si>
+  <si>
+    <t>GHE456540</t>
+  </si>
+  <si>
+    <t>GHE456541</t>
+  </si>
+  <si>
+    <t>GHE456542</t>
+  </si>
+  <si>
+    <t>GHE456543</t>
+  </si>
+  <si>
+    <t>GHE456544</t>
+  </si>
+  <si>
+    <t>GHE456545</t>
+  </si>
+  <si>
+    <t>GHE456546</t>
+  </si>
+  <si>
+    <t>GHE456547</t>
+  </si>
+  <si>
+    <t>GHE456548</t>
+  </si>
+  <si>
+    <t>GHE456549</t>
+  </si>
+  <si>
+    <t>GHE456550</t>
+  </si>
+  <si>
+    <t>GHE456551</t>
+  </si>
+  <si>
+    <t>GHE456552</t>
+  </si>
+  <si>
+    <t>GHE456553</t>
+  </si>
+  <si>
+    <t>GHE456554</t>
+  </si>
+  <si>
+    <t>GHE456555</t>
+  </si>
+  <si>
+    <t>GHE456556</t>
+  </si>
+  <si>
+    <t>GHE456557</t>
+  </si>
+  <si>
+    <t>GHE456558</t>
+  </si>
+  <si>
+    <t>GHE456559</t>
+  </si>
+  <si>
+    <t>GHE456560</t>
+  </si>
+  <si>
+    <t>GHE456561</t>
+  </si>
+  <si>
+    <t>GHE456562</t>
+  </si>
+  <si>
+    <t>GHE456563</t>
+  </si>
+  <si>
+    <t>GHE456564</t>
+  </si>
+  <si>
+    <t>GHE456565</t>
+  </si>
+  <si>
+    <t>GHE456566</t>
+  </si>
+  <si>
+    <t>GHE456567</t>
+  </si>
+  <si>
+    <t>GHE456568</t>
+  </si>
+  <si>
+    <t>GHE456569</t>
+  </si>
+  <si>
+    <t>GHE456570</t>
+  </si>
+  <si>
+    <t>GHE456571</t>
+  </si>
+  <si>
+    <t>GHE456572</t>
+  </si>
+  <si>
+    <t>GHE456573</t>
+  </si>
+  <si>
+    <t>GHE456574</t>
+  </si>
+  <si>
+    <t>GHE456575</t>
+  </si>
+  <si>
+    <t>GHE456576</t>
+  </si>
+  <si>
+    <t>GHE456577</t>
+  </si>
+  <si>
+    <t>GHE456578</t>
+  </si>
+  <si>
+    <t>GHE456579</t>
+  </si>
+  <si>
+    <t>GHE456580</t>
+  </si>
+  <si>
+    <t>GHE456581</t>
+  </si>
+  <si>
+    <t>GHE456582</t>
+  </si>
+  <si>
+    <t>GHE456583</t>
+  </si>
+  <si>
+    <t>GHE456584</t>
+  </si>
+  <si>
+    <t>GHE456585</t>
+  </si>
+  <si>
+    <t>GHE456586</t>
+  </si>
+  <si>
+    <t>GHE456587</t>
+  </si>
+  <si>
+    <t>GHE456588</t>
+  </si>
+  <si>
+    <t>GHE456589</t>
+  </si>
+  <si>
+    <t>GHE456590</t>
+  </si>
+  <si>
+    <t>GHE456591</t>
+  </si>
+  <si>
+    <t>GHE456592</t>
+  </si>
+  <si>
+    <t>GHE456593</t>
+  </si>
+  <si>
+    <t>GHE456594</t>
+  </si>
+  <si>
+    <t>GHE456595</t>
+  </si>
+  <si>
+    <t>GHE456596</t>
+  </si>
+  <si>
+    <t>GHE456597</t>
+  </si>
+  <si>
+    <t>GHE456598</t>
+  </si>
+  <si>
+    <t>GHE456599</t>
+  </si>
+  <si>
+    <t>GHE456600</t>
+  </si>
+  <si>
+    <t>GHE456601</t>
+  </si>
+  <si>
+    <t>GHE456602</t>
+  </si>
+  <si>
+    <t>GHE456603</t>
+  </si>
+  <si>
+    <t>GHE456604</t>
+  </si>
+  <si>
+    <t>GHE456605</t>
+  </si>
+  <si>
+    <t>GHE456606</t>
+  </si>
+  <si>
+    <t>GHE456607</t>
+  </si>
+  <si>
+    <t>GHE456608</t>
+  </si>
+  <si>
+    <t>GHE456609</t>
+  </si>
+  <si>
+    <t>GHE456610</t>
+  </si>
+  <si>
+    <t>GHE456611</t>
+  </si>
+  <si>
+    <t>GHE456612</t>
+  </si>
+  <si>
+    <t>GHE456613</t>
+  </si>
+  <si>
+    <t>GHE456614</t>
+  </si>
+  <si>
+    <t>GHE456615</t>
+  </si>
+  <si>
+    <t>GHE456616</t>
+  </si>
+  <si>
+    <t>GHE456617</t>
+  </si>
+  <si>
+    <t>GHE456618</t>
+  </si>
+  <si>
+    <t>GHE456619</t>
+  </si>
+  <si>
+    <t>GHE456620</t>
+  </si>
+  <si>
+    <t>GHE456621</t>
+  </si>
+  <si>
+    <t>GHE456622</t>
+  </si>
+  <si>
+    <t>GHE456623</t>
+  </si>
+  <si>
+    <t>GHE456624</t>
+  </si>
+  <si>
+    <t>GHE456625</t>
+  </si>
+  <si>
+    <t>GHE456626</t>
+  </si>
+  <si>
+    <t>GHE456627</t>
+  </si>
+  <si>
+    <t>GHE456628</t>
+  </si>
+  <si>
+    <t>GHE456629</t>
+  </si>
+  <si>
+    <t>GHE456630</t>
+  </si>
+  <si>
+    <t>GHE456631</t>
+  </si>
+  <si>
+    <t>GHE456632</t>
+  </si>
+  <si>
+    <t>GHE456633</t>
+  </si>
+  <si>
+    <t>GHE456634</t>
+  </si>
+  <si>
+    <t>GHE456635</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N450"/>
+  <dimension ref="A1:N461"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="15.33203125" customWidth="1"/>
@@ -11484,7 +12039,7 @@
         <v>456435</v>
       </c>
       <c r="N261" t="str">
-        <f t="shared" ref="N261:N276" si="4">K261&amp;L261</f>
+        <f t="shared" ref="N261:N324" si="4">K261&amp;L261</f>
         <v>GHE456435</v>
       </c>
     </row>
@@ -12080,17 +12635,36 @@
       <c r="B277" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C277" s="6">
+        <v>9893791001</v>
+      </c>
       <c r="D277" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E277" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F277" s="5">
+        <v>47678965671</v>
+      </c>
       <c r="G277" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I277" t="s">
+        <v>289</v>
+      </c>
+      <c r="K277" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L277">
+        <v>456451</v>
+      </c>
+      <c r="N277" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456451</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
@@ -12100,17 +12674,36 @@
       <c r="B278" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C278" s="6">
+        <v>9893791002</v>
+      </c>
       <c r="D278" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E278" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F278" s="5">
+        <v>47678965672</v>
+      </c>
       <c r="G278" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I278" t="s">
+        <v>290</v>
+      </c>
+      <c r="K278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L278">
+        <v>456452</v>
+      </c>
+      <c r="N278" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456452</v>
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
@@ -12120,17 +12713,36 @@
       <c r="B279" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C279" s="6">
+        <v>9893791003</v>
+      </c>
       <c r="D279" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E279" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F279" s="5">
+        <v>47678965673</v>
+      </c>
       <c r="G279" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H279" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I279" t="s">
+        <v>291</v>
+      </c>
+      <c r="K279" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L279">
+        <v>456453</v>
+      </c>
+      <c r="N279" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456453</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
@@ -12140,17 +12752,36 @@
       <c r="B280" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C280" s="6">
+        <v>9893791004</v>
+      </c>
       <c r="D280" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E280" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F280" s="5">
+        <v>47678965674</v>
+      </c>
       <c r="G280" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I280" t="s">
+        <v>292</v>
+      </c>
+      <c r="K280" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L280">
+        <v>456454</v>
+      </c>
+      <c r="N280" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456454</v>
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
@@ -12160,17 +12791,36 @@
       <c r="B281" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C281" s="6">
+        <v>9893791005</v>
+      </c>
       <c r="D281" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F281" s="5">
+        <v>47678965675</v>
+      </c>
       <c r="G281" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I281" t="s">
+        <v>293</v>
+      </c>
+      <c r="K281" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L281">
+        <v>456455</v>
+      </c>
+      <c r="N281" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456455</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
@@ -12180,17 +12830,36 @@
       <c r="B282" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C282" s="6">
+        <v>9893791006</v>
+      </c>
       <c r="D282" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F282" s="5">
+        <v>47678965676</v>
+      </c>
       <c r="G282" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I282" t="s">
+        <v>294</v>
+      </c>
+      <c r="K282" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L282">
+        <v>456456</v>
+      </c>
+      <c r="N282" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456456</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
@@ -12200,17 +12869,36 @@
       <c r="B283" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C283" s="6">
+        <v>9893791007</v>
+      </c>
       <c r="D283" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F283" s="5">
+        <v>47678965677</v>
+      </c>
       <c r="G283" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I283" t="s">
+        <v>295</v>
+      </c>
+      <c r="K283" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L283">
+        <v>456457</v>
+      </c>
+      <c r="N283" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456457</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
@@ -12220,17 +12908,36 @@
       <c r="B284" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C284" s="6">
+        <v>9893791008</v>
+      </c>
       <c r="D284" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E284" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F284" s="5">
+        <v>47678965678</v>
+      </c>
       <c r="G284" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I284" t="s">
+        <v>296</v>
+      </c>
+      <c r="K284" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L284">
+        <v>456458</v>
+      </c>
+      <c r="N284" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456458</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
@@ -12240,17 +12947,36 @@
       <c r="B285" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C285" s="6">
+        <v>9893791009</v>
+      </c>
       <c r="D285" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E285" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F285" s="5">
+        <v>47678965679</v>
+      </c>
       <c r="G285" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I285" t="s">
+        <v>297</v>
+      </c>
+      <c r="K285" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L285">
+        <v>456459</v>
+      </c>
+      <c r="N285" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456459</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
@@ -12260,17 +12986,36 @@
       <c r="B286" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C286" s="6">
+        <v>9893791010</v>
+      </c>
       <c r="D286" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E286" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F286" s="5">
+        <v>47678965680</v>
+      </c>
       <c r="G286" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I286" t="s">
+        <v>298</v>
+      </c>
+      <c r="K286" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L286">
+        <v>456460</v>
+      </c>
+      <c r="N286" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456460</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
@@ -12280,17 +13025,36 @@
       <c r="B287" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C287" s="6">
+        <v>9893791011</v>
+      </c>
       <c r="D287" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F287" s="5">
+        <v>47678965681</v>
+      </c>
       <c r="G287" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I287" t="s">
+        <v>299</v>
+      </c>
+      <c r="K287" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L287">
+        <v>456461</v>
+      </c>
+      <c r="N287" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456461</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
@@ -12300,3257 +13064,6783 @@
       <c r="B288" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C288" s="6">
+        <v>9893791012</v>
+      </c>
       <c r="D288" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E288" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F288" s="5">
+        <v>47678965682</v>
+      </c>
       <c r="G288" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I288" t="s">
+        <v>300</v>
+      </c>
+      <c r="K288" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L288">
+        <v>456462</v>
+      </c>
+      <c r="N288" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456462</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C289" s="6">
+        <v>9893791013</v>
+      </c>
       <c r="D289" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E289" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F289" s="5">
+        <v>47678965683</v>
+      </c>
       <c r="G289" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I289" t="s">
+        <v>301</v>
+      </c>
+      <c r="K289" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L289">
+        <v>456463</v>
+      </c>
+      <c r="N289" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456463</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C290" s="6">
+        <v>9893791014</v>
+      </c>
       <c r="D290" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E290" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F290" s="5">
+        <v>47678965684</v>
+      </c>
       <c r="G290" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I290" t="s">
+        <v>302</v>
+      </c>
+      <c r="K290" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L290">
+        <v>456464</v>
+      </c>
+      <c r="N290" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456464</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C291" s="6">
+        <v>9893791015</v>
+      </c>
       <c r="D291" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E291" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F291" s="5">
+        <v>47678965685</v>
+      </c>
       <c r="G291" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I291" t="s">
+        <v>303</v>
+      </c>
+      <c r="K291" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L291">
+        <v>456465</v>
+      </c>
+      <c r="N291" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456465</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C292" s="6">
+        <v>9893791016</v>
+      </c>
       <c r="D292" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E292" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F292" s="5">
+        <v>47678965686</v>
+      </c>
       <c r="G292" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I292" t="s">
+        <v>304</v>
+      </c>
+      <c r="K292" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L292">
+        <v>456466</v>
+      </c>
+      <c r="N292" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456466</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C293" s="6">
+        <v>9893791017</v>
+      </c>
       <c r="D293" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E293" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F293" s="5">
+        <v>47678965687</v>
+      </c>
       <c r="G293" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I293" t="s">
+        <v>305</v>
+      </c>
+      <c r="K293" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L293">
+        <v>456467</v>
+      </c>
+      <c r="N293" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456467</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C294" s="6">
+        <v>9893791018</v>
+      </c>
       <c r="D294" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E294" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F294" s="5">
+        <v>47678965688</v>
+      </c>
       <c r="G294" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I294" t="s">
+        <v>306</v>
+      </c>
+      <c r="K294" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L294">
+        <v>456468</v>
+      </c>
+      <c r="N294" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456468</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C295" s="6">
+        <v>9893791019</v>
+      </c>
       <c r="D295" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E295" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F295" s="5">
+        <v>47678965689</v>
+      </c>
       <c r="G295" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I295" t="s">
+        <v>307</v>
+      </c>
+      <c r="K295" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L295">
+        <v>456469</v>
+      </c>
+      <c r="N295" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456469</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C296" s="6">
+        <v>9893791020</v>
+      </c>
       <c r="D296" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E296" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F296" s="5">
+        <v>47678965690</v>
+      </c>
       <c r="G296" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I296" t="s">
+        <v>308</v>
+      </c>
+      <c r="K296" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L296">
+        <v>456470</v>
+      </c>
+      <c r="N296" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456470</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C297" s="6">
+        <v>9893791021</v>
+      </c>
       <c r="D297" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F297" s="5">
+        <v>47678965691</v>
+      </c>
       <c r="G297" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I297" t="s">
+        <v>309</v>
+      </c>
+      <c r="K297" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L297">
+        <v>456471</v>
+      </c>
+      <c r="N297" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456471</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C298" s="6">
+        <v>9893791022</v>
+      </c>
       <c r="D298" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E298" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F298" s="5">
+        <v>47678965692</v>
+      </c>
       <c r="G298" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I298" t="s">
+        <v>310</v>
+      </c>
+      <c r="K298" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L298">
+        <v>456472</v>
+      </c>
+      <c r="N298" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456472</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C299" s="6">
+        <v>9893791023</v>
+      </c>
       <c r="D299" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E299" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F299" s="5">
+        <v>47678965693</v>
+      </c>
       <c r="G299" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I299" t="s">
+        <v>311</v>
+      </c>
+      <c r="K299" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L299">
+        <v>456473</v>
+      </c>
+      <c r="N299" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456473</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C300" s="6">
+        <v>9893791024</v>
+      </c>
       <c r="D300" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F300" s="5">
+        <v>47678965694</v>
+      </c>
       <c r="G300" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I300" t="s">
+        <v>312</v>
+      </c>
+      <c r="K300" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L300">
+        <v>456474</v>
+      </c>
+      <c r="N300" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456474</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C301" s="6">
+        <v>9893791025</v>
+      </c>
       <c r="D301" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E301" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F301" s="5">
+        <v>47678965695</v>
+      </c>
       <c r="G301" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I301" t="s">
+        <v>313</v>
+      </c>
+      <c r="K301" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L301">
+        <v>456475</v>
+      </c>
+      <c r="N301" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456475</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C302" s="6">
+        <v>9893791026</v>
+      </c>
       <c r="D302" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E302" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F302" s="5">
+        <v>47678965696</v>
+      </c>
       <c r="G302" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H302" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I302" t="s">
+        <v>314</v>
+      </c>
+      <c r="K302" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L302">
+        <v>456476</v>
+      </c>
+      <c r="N302" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456476</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C303" s="6">
+        <v>9893791027</v>
+      </c>
       <c r="D303" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E303" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F303" s="5">
+        <v>47678965697</v>
+      </c>
       <c r="G303" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H303" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I303" t="s">
+        <v>315</v>
+      </c>
+      <c r="K303" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L303">
+        <v>456477</v>
+      </c>
+      <c r="N303" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456477</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C304" s="6">
+        <v>9893791028</v>
+      </c>
       <c r="D304" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E304" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F304" s="5">
+        <v>47678965698</v>
+      </c>
       <c r="G304" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H304" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I304" t="s">
+        <v>316</v>
+      </c>
+      <c r="K304" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L304">
+        <v>456478</v>
+      </c>
+      <c r="N304" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456478</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C305" s="6">
+        <v>9893791029</v>
+      </c>
       <c r="D305" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E305" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F305" s="5">
+        <v>47678965699</v>
+      </c>
       <c r="G305" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H305" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I305" t="s">
+        <v>317</v>
+      </c>
+      <c r="K305" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L305">
+        <v>456479</v>
+      </c>
+      <c r="N305" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456479</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C306" s="6">
+        <v>9893791030</v>
+      </c>
       <c r="D306" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E306" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F306" s="5">
+        <v>47678965700</v>
+      </c>
       <c r="G306" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H306" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I306" t="s">
+        <v>318</v>
+      </c>
+      <c r="K306" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L306">
+        <v>456480</v>
+      </c>
+      <c r="N306" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456480</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C307" s="6">
+        <v>9893791031</v>
+      </c>
       <c r="D307" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E307" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F307" s="5">
+        <v>47678965701</v>
+      </c>
       <c r="G307" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H307" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I307" t="s">
+        <v>319</v>
+      </c>
+      <c r="K307" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L307">
+        <v>456481</v>
+      </c>
+      <c r="N307" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456481</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C308" s="6">
+        <v>9893791032</v>
+      </c>
       <c r="D308" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E308" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F308" s="5">
+        <v>47678965702</v>
+      </c>
       <c r="G308" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H308" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I308" t="s">
+        <v>320</v>
+      </c>
+      <c r="K308" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L308">
+        <v>456482</v>
+      </c>
+      <c r="N308" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456482</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C309" s="6">
+        <v>9893791033</v>
+      </c>
       <c r="D309" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E309" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F309" s="5">
+        <v>47678965703</v>
+      </c>
       <c r="G309" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H309" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I309" t="s">
+        <v>321</v>
+      </c>
+      <c r="K309" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L309">
+        <v>456483</v>
+      </c>
+      <c r="N309" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456483</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C310" s="6">
+        <v>9893791034</v>
+      </c>
       <c r="D310" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E310" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F310" s="5">
+        <v>47678965704</v>
+      </c>
       <c r="G310" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H310" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I310" t="s">
+        <v>322</v>
+      </c>
+      <c r="K310" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L310">
+        <v>456484</v>
+      </c>
+      <c r="N310" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456484</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C311" s="6">
+        <v>9893791035</v>
+      </c>
       <c r="D311" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E311" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F311" s="5">
+        <v>47678965705</v>
+      </c>
       <c r="G311" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H311" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I311" t="s">
+        <v>323</v>
+      </c>
+      <c r="K311" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L311">
+        <v>456485</v>
+      </c>
+      <c r="N311" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456485</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C312" s="6">
+        <v>9893791036</v>
+      </c>
       <c r="D312" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E312" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F312" s="5">
+        <v>47678965706</v>
+      </c>
       <c r="G312" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H312" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I312" t="s">
+        <v>324</v>
+      </c>
+      <c r="K312" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L312">
+        <v>456486</v>
+      </c>
+      <c r="N312" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456486</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C313" s="6">
+        <v>9893791037</v>
+      </c>
       <c r="D313" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E313" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F313" s="5">
+        <v>47678965707</v>
+      </c>
       <c r="G313" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H313" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I313" t="s">
+        <v>325</v>
+      </c>
+      <c r="K313" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L313">
+        <v>456487</v>
+      </c>
+      <c r="N313" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456487</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B314" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C314" s="6">
+        <v>9893791038</v>
+      </c>
       <c r="D314" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E314" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F314" s="5">
+        <v>47678965708</v>
+      </c>
       <c r="G314" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H314" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I314" t="s">
+        <v>326</v>
+      </c>
+      <c r="K314" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L314">
+        <v>456488</v>
+      </c>
+      <c r="N314" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456488</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B315" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C315" s="6">
+        <v>9893791039</v>
+      </c>
       <c r="D315" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E315" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F315" s="5">
+        <v>47678965709</v>
+      </c>
       <c r="G315" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H315" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I315" t="s">
+        <v>327</v>
+      </c>
+      <c r="K315" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L315">
+        <v>456489</v>
+      </c>
+      <c r="N315" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456489</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B316" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C316" s="6">
+        <v>9893791040</v>
+      </c>
       <c r="D316" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E316" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F316" s="5">
+        <v>47678965710</v>
+      </c>
       <c r="G316" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H316" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I316" t="s">
+        <v>328</v>
+      </c>
+      <c r="K316" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L316">
+        <v>456490</v>
+      </c>
+      <c r="N316" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456490</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B317" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C317" s="6">
+        <v>9893791041</v>
+      </c>
       <c r="D317" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E317" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F317" s="5">
+        <v>47678965711</v>
+      </c>
       <c r="G317" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H317" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I317" t="s">
+        <v>329</v>
+      </c>
+      <c r="K317" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L317">
+        <v>456491</v>
+      </c>
+      <c r="N317" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456491</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B318" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C318" s="6">
+        <v>9893791042</v>
+      </c>
       <c r="D318" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E318" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F318" s="5">
+        <v>47678965712</v>
+      </c>
       <c r="G318" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H318" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I318" t="s">
+        <v>330</v>
+      </c>
+      <c r="K318" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L318">
+        <v>456492</v>
+      </c>
+      <c r="N318" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456492</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C319" s="6">
+        <v>9893791043</v>
+      </c>
       <c r="D319" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E319" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F319" s="5">
+        <v>47678965713</v>
+      </c>
       <c r="G319" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H319" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I319" t="s">
+        <v>331</v>
+      </c>
+      <c r="K319" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L319">
+        <v>456493</v>
+      </c>
+      <c r="N319" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456493</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C320" s="6">
+        <v>9893791044</v>
+      </c>
       <c r="D320" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E320" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F320" s="5">
+        <v>47678965714</v>
+      </c>
       <c r="G320" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H320" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I320" t="s">
+        <v>332</v>
+      </c>
+      <c r="K320" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L320">
+        <v>456494</v>
+      </c>
+      <c r="N320" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456494</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B321" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C321" s="6">
+        <v>9893791045</v>
+      </c>
       <c r="D321" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E321" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F321" s="5">
+        <v>47678965715</v>
+      </c>
       <c r="G321" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H321" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I321" t="s">
+        <v>333</v>
+      </c>
+      <c r="K321" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L321">
+        <v>456495</v>
+      </c>
+      <c r="N321" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456495</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C322" s="6">
+        <v>9893791046</v>
+      </c>
       <c r="D322" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E322" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F322" s="5">
+        <v>47678965716</v>
+      </c>
       <c r="G322" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H322" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I322" t="s">
+        <v>334</v>
+      </c>
+      <c r="K322" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L322">
+        <v>456496</v>
+      </c>
+      <c r="N322" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456496</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C323" s="6">
+        <v>9893791047</v>
+      </c>
       <c r="D323" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E323" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F323" s="5">
+        <v>47678965717</v>
+      </c>
       <c r="G323" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H323" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I323" t="s">
+        <v>335</v>
+      </c>
+      <c r="K323" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L323">
+        <v>456497</v>
+      </c>
+      <c r="N323" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456497</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C324" s="6">
+        <v>9893791048</v>
+      </c>
       <c r="D324" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E324" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F324" s="5">
+        <v>47678965718</v>
+      </c>
       <c r="G324" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H324" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I324" t="s">
+        <v>336</v>
+      </c>
+      <c r="K324" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L324">
+        <v>456498</v>
+      </c>
+      <c r="N324" t="str">
+        <f t="shared" si="4"/>
+        <v>GHE456498</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B325" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C325" s="6">
+        <v>9893791049</v>
+      </c>
       <c r="D325" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F325" s="5">
+        <v>47678965719</v>
+      </c>
       <c r="G325" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H325" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I325" t="s">
+        <v>337</v>
+      </c>
+      <c r="K325" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L325">
+        <v>456499</v>
+      </c>
+      <c r="N325" t="str">
+        <f t="shared" ref="N325:N391" si="5">K325&amp;L325</f>
+        <v>GHE456499</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B326" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C326" s="6">
+        <v>9893791050</v>
+      </c>
       <c r="D326" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E326" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F326" s="5">
+        <v>47678965720</v>
+      </c>
       <c r="G326" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H326" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I326" t="s">
+        <v>338</v>
+      </c>
+      <c r="K326" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L326">
+        <v>456500</v>
+      </c>
+      <c r="N326" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456500</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B327" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C327" s="6">
+        <v>9893791051</v>
+      </c>
       <c r="D327" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E327" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F327" s="5">
+        <v>47678965721</v>
+      </c>
       <c r="G327" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H327" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I327" t="s">
+        <v>339</v>
+      </c>
+      <c r="K327" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L327">
+        <v>456501</v>
+      </c>
+      <c r="N327" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456501</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B328" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C328" s="6">
+        <v>9893791052</v>
+      </c>
       <c r="D328" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E328" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F328" s="5">
+        <v>47678965722</v>
+      </c>
       <c r="G328" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H328" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I328" t="s">
+        <v>340</v>
+      </c>
+      <c r="K328" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L328">
+        <v>456502</v>
+      </c>
+      <c r="N328" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456502</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C329" s="6">
+        <v>9893791053</v>
+      </c>
       <c r="D329" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E329" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F329" s="5">
+        <v>47678965723</v>
+      </c>
       <c r="G329" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H329" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I329" t="s">
+        <v>341</v>
+      </c>
+      <c r="K329" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L329">
+        <v>456503</v>
+      </c>
+      <c r="N329" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456503</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B330" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C330" s="6">
+        <v>9893791054</v>
+      </c>
       <c r="D330" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E330" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F330" s="5">
+        <v>47678965724</v>
+      </c>
       <c r="G330" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H330" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I330" t="s">
+        <v>342</v>
+      </c>
+      <c r="K330" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L330">
+        <v>456504</v>
+      </c>
+      <c r="N330" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456504</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C331" s="6">
+        <v>9893791055</v>
+      </c>
       <c r="D331" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E331" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F331" s="5">
+        <v>47678965725</v>
+      </c>
       <c r="G331" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H331" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I331" t="s">
+        <v>343</v>
+      </c>
+      <c r="K331" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L331">
+        <v>456505</v>
+      </c>
+      <c r="N331" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456505</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B332" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C332" s="6">
+        <v>9893791056</v>
+      </c>
       <c r="D332" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E332" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F332" s="5">
+        <v>47678965726</v>
+      </c>
       <c r="G332" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H332" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I332" t="s">
+        <v>344</v>
+      </c>
+      <c r="K332" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L332">
+        <v>456506</v>
+      </c>
+      <c r="N332" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456506</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C333" s="6">
+        <v>9893791057</v>
+      </c>
       <c r="D333" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E333" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F333" s="5">
+        <v>47678965727</v>
+      </c>
       <c r="G333" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H333" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I333" t="s">
+        <v>345</v>
+      </c>
+      <c r="K333" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L333">
+        <v>456507</v>
+      </c>
+      <c r="N333" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456507</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B334" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C334" s="6">
+        <v>9893791058</v>
+      </c>
       <c r="D334" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E334" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F334" s="5">
+        <v>47678965728</v>
+      </c>
       <c r="G334" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H334" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I334" t="s">
+        <v>346</v>
+      </c>
+      <c r="K334" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L334">
+        <v>456508</v>
+      </c>
+      <c r="N334" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456508</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B335" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C335" s="6">
+        <v>9893791059</v>
+      </c>
       <c r="D335" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E335" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F335" s="5">
+        <v>47678965729</v>
+      </c>
       <c r="G335" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H335" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I335" t="s">
+        <v>347</v>
+      </c>
+      <c r="K335" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L335">
+        <v>456509</v>
+      </c>
+      <c r="N335" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456509</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B336" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C336" s="6">
+        <v>9893791060</v>
+      </c>
       <c r="D336" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E336" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F336" s="5">
+        <v>47678965730</v>
+      </c>
       <c r="G336" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H336" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I336" t="s">
+        <v>348</v>
+      </c>
+      <c r="K336" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L336">
+        <v>456510</v>
+      </c>
+      <c r="N336" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456510</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B337" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C337" s="6">
+        <v>9893791061</v>
+      </c>
       <c r="D337" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E337" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F337" s="5">
+        <v>47678965731</v>
+      </c>
       <c r="G337" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H337" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I337" t="s">
+        <v>349</v>
+      </c>
+      <c r="K337" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L337">
+        <v>456511</v>
+      </c>
+      <c r="N337" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456511</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B338" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C338" s="6">
+        <v>9893791062</v>
+      </c>
       <c r="D338" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E338" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F338" s="5">
+        <v>47678965732</v>
+      </c>
       <c r="G338" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H338" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I338" t="s">
+        <v>350</v>
+      </c>
+      <c r="K338" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L338">
+        <v>456512</v>
+      </c>
+      <c r="N338" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456512</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B339" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C339" s="6">
+        <v>9893791063</v>
+      </c>
       <c r="D339" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E339" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F339" s="5">
+        <v>47678965733</v>
+      </c>
       <c r="G339" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H339" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I339" t="s">
+        <v>351</v>
+      </c>
+      <c r="K339" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L339">
+        <v>456513</v>
+      </c>
+      <c r="N339" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456513</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B340" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C340" s="6">
+        <v>9893791064</v>
+      </c>
       <c r="D340" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E340" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F340" s="5">
+        <v>47678965734</v>
+      </c>
       <c r="G340" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H340" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I340" t="s">
+        <v>352</v>
+      </c>
+      <c r="K340" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L340">
+        <v>456514</v>
+      </c>
+      <c r="N340" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456514</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B341" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C341" s="6">
+        <v>9893791065</v>
+      </c>
       <c r="D341" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E341" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F341" s="5">
+        <v>47678965735</v>
+      </c>
       <c r="G341" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H341" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I341" t="s">
+        <v>353</v>
+      </c>
+      <c r="K341" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L341">
+        <v>456515</v>
+      </c>
+      <c r="N341" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456515</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C342" s="6">
+        <v>9893791066</v>
+      </c>
       <c r="D342" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E342" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F342" s="5">
+        <v>47678965736</v>
+      </c>
       <c r="G342" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H342" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I342" t="s">
+        <v>354</v>
+      </c>
+      <c r="K342" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L342">
+        <v>456516</v>
+      </c>
+      <c r="N342" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456516</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C343" s="6">
+        <v>9893791067</v>
+      </c>
       <c r="D343" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E343" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F343" s="5">
+        <v>47678965737</v>
+      </c>
       <c r="G343" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H343" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I343" t="s">
+        <v>355</v>
+      </c>
+      <c r="K343" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L343">
+        <v>456517</v>
+      </c>
+      <c r="N343" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456517</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B344" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C344" s="6">
+        <v>9893791068</v>
+      </c>
       <c r="D344" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E344" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F344" s="5">
+        <v>47678965738</v>
+      </c>
       <c r="G344" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H344" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I344" t="s">
+        <v>356</v>
+      </c>
+      <c r="K344" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L344">
+        <v>456518</v>
+      </c>
+      <c r="N344" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456518</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B345" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C345" s="6">
+        <v>9893791069</v>
+      </c>
       <c r="D345" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E345" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F345" s="5">
+        <v>47678965739</v>
+      </c>
       <c r="G345" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H345" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I345" t="s">
+        <v>357</v>
+      </c>
+      <c r="K345" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L345">
+        <v>456519</v>
+      </c>
+      <c r="N345" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456519</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C346" s="6">
+        <v>9893791070</v>
+      </c>
       <c r="D346" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E346" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F346" s="5">
+        <v>47678965740</v>
+      </c>
       <c r="G346" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H346" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I346" t="s">
+        <v>358</v>
+      </c>
+      <c r="K346" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L346">
+        <v>456520</v>
+      </c>
+      <c r="N346" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456520</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B347" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C347" s="6">
+        <v>9893791071</v>
+      </c>
       <c r="D347" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E347" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F347" s="5">
+        <v>47678965741</v>
+      </c>
       <c r="G347" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H347" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I347" t="s">
+        <v>359</v>
+      </c>
+      <c r="K347" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L347">
+        <v>456521</v>
+      </c>
+      <c r="N347" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456521</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B348" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C348" s="6">
+        <v>9893791072</v>
+      </c>
       <c r="D348" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E348" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F348" s="5">
+        <v>47678965742</v>
+      </c>
       <c r="G348" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H348" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I348" t="s">
+        <v>360</v>
+      </c>
+      <c r="K348" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L348">
+        <v>456522</v>
+      </c>
+      <c r="N348" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456522</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C349" s="6">
+        <v>9893791073</v>
+      </c>
       <c r="D349" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E349" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F349" s="5">
+        <v>47678965743</v>
+      </c>
       <c r="G349" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H349" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I349" t="s">
+        <v>361</v>
+      </c>
+      <c r="K349" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L349">
+        <v>456523</v>
+      </c>
+      <c r="N349" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456523</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C350" s="6">
+        <v>9893791074</v>
+      </c>
       <c r="D350" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E350" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F350" s="5">
+        <v>47678965744</v>
+      </c>
       <c r="G350" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H350" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I350" t="s">
+        <v>362</v>
+      </c>
+      <c r="K350" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L350">
+        <v>456524</v>
+      </c>
+      <c r="N350" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456524</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C351" s="6">
+        <v>9893791075</v>
+      </c>
       <c r="D351" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E351" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F351" s="5">
+        <v>47678965745</v>
+      </c>
       <c r="G351" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H351" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I351" t="s">
+        <v>363</v>
+      </c>
+      <c r="K351" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L351">
+        <v>456525</v>
+      </c>
+      <c r="N351" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456525</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C352" s="6">
+        <v>9893791076</v>
+      </c>
       <c r="D352" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E352" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F352" s="5">
+        <v>47678965746</v>
+      </c>
       <c r="G352" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H352" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I352" t="s">
+        <v>364</v>
+      </c>
+      <c r="K352" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L352">
+        <v>456526</v>
+      </c>
+      <c r="N352" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456526</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C353" s="6">
+        <v>9893791077</v>
+      </c>
       <c r="D353" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E353" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F353" s="5">
+        <v>47678965747</v>
+      </c>
       <c r="G353" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H353" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I353" t="s">
+        <v>365</v>
+      </c>
+      <c r="K353" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L353">
+        <v>456527</v>
+      </c>
+      <c r="N353" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456527</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C354" s="6">
+        <v>9893791078</v>
+      </c>
       <c r="D354" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E354" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F354" s="5">
+        <v>47678965748</v>
+      </c>
       <c r="G354" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H354" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I354" t="s">
+        <v>366</v>
+      </c>
+      <c r="K354" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L354">
+        <v>456528</v>
+      </c>
+      <c r="N354" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456528</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B355" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C355" s="6">
+        <v>9893791079</v>
+      </c>
       <c r="D355" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E355" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F355" s="5">
+        <v>47678965749</v>
+      </c>
       <c r="G355" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H355" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I355" t="s">
+        <v>367</v>
+      </c>
+      <c r="K355" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L355">
+        <v>456529</v>
+      </c>
+      <c r="N355" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456529</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B356" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C356" s="6">
+        <v>9893791080</v>
+      </c>
       <c r="D356" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E356" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F356" s="5">
+        <v>47678965750</v>
+      </c>
       <c r="G356" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H356" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I356" t="s">
+        <v>368</v>
+      </c>
+      <c r="K356" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L356">
+        <v>456530</v>
+      </c>
+      <c r="N356" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456530</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B357" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C357" s="6">
+        <v>9893791081</v>
+      </c>
       <c r="D357" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E357" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F357" s="5">
+        <v>47678965751</v>
+      </c>
       <c r="G357" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H357" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I357" t="s">
+        <v>369</v>
+      </c>
+      <c r="K357" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L357">
+        <v>456531</v>
+      </c>
+      <c r="N357" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456531</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C358" s="6">
+        <v>9893791082</v>
+      </c>
       <c r="D358" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E358" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F358" s="5">
+        <v>47678965752</v>
+      </c>
       <c r="G358" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H358" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I358" t="s">
+        <v>370</v>
+      </c>
+      <c r="K358" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L358">
+        <v>456532</v>
+      </c>
+      <c r="N358" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456532</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C359" s="6">
+        <v>9893791083</v>
+      </c>
       <c r="D359" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E359" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F359" s="5">
+        <v>47678965753</v>
+      </c>
       <c r="G359" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H359" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I359" t="s">
+        <v>371</v>
+      </c>
+      <c r="K359" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L359">
+        <v>456533</v>
+      </c>
+      <c r="N359" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456533</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C360" s="6">
+        <v>9893791084</v>
+      </c>
       <c r="D360" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E360" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F360" s="5">
+        <v>47678965754</v>
+      </c>
       <c r="G360" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H360" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I360" t="s">
+        <v>372</v>
+      </c>
+      <c r="K360" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L360">
+        <v>456534</v>
+      </c>
+      <c r="N360" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456534</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C361" s="6">
+        <v>9893791085</v>
+      </c>
       <c r="D361" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E361" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F361" s="5">
+        <v>47678965755</v>
+      </c>
       <c r="G361" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H361" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I361" t="s">
+        <v>373</v>
+      </c>
+      <c r="K361" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L361">
+        <v>456535</v>
+      </c>
+      <c r="N361" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456535</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C362" s="6">
+        <v>9893791086</v>
+      </c>
       <c r="D362" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E362" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F362" s="5">
+        <v>47678965756</v>
+      </c>
       <c r="G362" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H362" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I362" t="s">
+        <v>374</v>
+      </c>
+      <c r="K362" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L362">
+        <v>456536</v>
+      </c>
+      <c r="N362" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456536</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C363" s="6">
+        <v>9893791087</v>
+      </c>
       <c r="D363" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E363" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F363" s="5">
+        <v>47678965757</v>
+      </c>
       <c r="G363" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H363" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I363" t="s">
+        <v>375</v>
+      </c>
+      <c r="K363" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L363">
+        <v>456537</v>
+      </c>
+      <c r="N363" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456537</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B364" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C364" s="6">
+        <v>9893791088</v>
+      </c>
       <c r="D364" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E364" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F364" s="5">
+        <v>47678965758</v>
+      </c>
       <c r="G364" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H364" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I364" t="s">
+        <v>376</v>
+      </c>
+      <c r="K364" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L364">
+        <v>456538</v>
+      </c>
+      <c r="N364" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456538</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C365" s="6">
+        <v>9893791089</v>
+      </c>
       <c r="D365" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E365" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F365" s="5">
+        <v>47678965759</v>
+      </c>
       <c r="G365" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H365" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I365" t="s">
+        <v>377</v>
+      </c>
+      <c r="K365" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L365">
+        <v>456539</v>
+      </c>
+      <c r="N365" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456539</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C366" s="6">
+        <v>9893791090</v>
+      </c>
       <c r="D366" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E366" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F366" s="5">
+        <v>47678965760</v>
+      </c>
       <c r="G366" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H366" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I366" t="s">
+        <v>378</v>
+      </c>
+      <c r="K366" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L366">
+        <v>456540</v>
+      </c>
+      <c r="N366" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456540</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B367" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C367" s="6">
+        <v>9893791091</v>
+      </c>
       <c r="D367" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E367" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F367" s="5">
+        <v>47678965761</v>
+      </c>
       <c r="G367" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H367" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I367" t="s">
+        <v>379</v>
+      </c>
+      <c r="K367" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L367">
+        <v>456541</v>
+      </c>
+      <c r="N367" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456541</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B368" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C368" s="6">
+        <v>9893791092</v>
+      </c>
       <c r="D368" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E368" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F368" s="5">
+        <v>47678965762</v>
+      </c>
       <c r="G368" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H368" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I368" t="s">
+        <v>380</v>
+      </c>
+      <c r="K368" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L368">
+        <v>456542</v>
+      </c>
+      <c r="N368" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456542</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B369" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C369" s="6">
+        <v>9893791093</v>
+      </c>
       <c r="D369" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E369" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F369" s="5">
+        <v>47678965763</v>
+      </c>
       <c r="G369" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H369" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I369" t="s">
+        <v>381</v>
+      </c>
+      <c r="K369" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L369">
+        <v>456543</v>
+      </c>
+      <c r="N369" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456543</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B370" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C370" s="6">
+        <v>9893791094</v>
+      </c>
       <c r="D370" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E370" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F370" s="5">
+        <v>47678965764</v>
+      </c>
       <c r="G370" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H370" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I370" t="s">
+        <v>382</v>
+      </c>
+      <c r="K370" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L370">
+        <v>456544</v>
+      </c>
+      <c r="N370" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456544</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C371" s="6">
+        <v>9893791095</v>
+      </c>
       <c r="D371" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E371" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F371" s="5">
+        <v>47678965765</v>
+      </c>
       <c r="G371" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H371" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I371" t="s">
+        <v>383</v>
+      </c>
+      <c r="K371" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L371">
+        <v>456545</v>
+      </c>
+      <c r="N371" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456545</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C372" s="6">
+        <v>9893791096</v>
+      </c>
       <c r="D372" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E372" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F372" s="5">
+        <v>47678965766</v>
+      </c>
       <c r="G372" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H372" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I372" t="s">
+        <v>384</v>
+      </c>
+      <c r="K372" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L372">
+        <v>456546</v>
+      </c>
+      <c r="N372" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456546</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C373" s="6">
+        <v>9893791097</v>
+      </c>
       <c r="D373" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E373" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F373" s="5">
+        <v>47678965767</v>
+      </c>
       <c r="G373" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H373" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I373" t="s">
+        <v>385</v>
+      </c>
+      <c r="K373" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L373">
+        <v>456547</v>
+      </c>
+      <c r="N373" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456547</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C374" s="6">
+        <v>9893791098</v>
+      </c>
       <c r="D374" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E374" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F374" s="5">
+        <v>47678965768</v>
+      </c>
       <c r="G374" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H374" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I374" t="s">
+        <v>386</v>
+      </c>
+      <c r="K374" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L374">
+        <v>456548</v>
+      </c>
+      <c r="N374" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456548</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B375" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C375" s="6">
+        <v>9893791099</v>
+      </c>
       <c r="D375" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E375" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F375" s="5">
+        <v>47678965769</v>
+      </c>
       <c r="G375" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H375" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I375" t="s">
+        <v>387</v>
+      </c>
+      <c r="K375" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L375">
+        <v>456549</v>
+      </c>
+      <c r="N375" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456549</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C376" s="6">
+        <v>9893791100</v>
+      </c>
       <c r="D376" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E376" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F376" s="5">
+        <v>47678965770</v>
+      </c>
       <c r="G376" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H376" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I376" t="s">
+        <v>388</v>
+      </c>
+      <c r="K376" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L376">
+        <v>456550</v>
+      </c>
+      <c r="N376" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456550</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C377" s="6">
+        <v>9893791101</v>
+      </c>
       <c r="D377" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E377" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F377" s="5">
+        <v>47678965771</v>
+      </c>
       <c r="G377" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H377" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I377" t="s">
+        <v>389</v>
+      </c>
+      <c r="K377" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L377">
+        <v>456551</v>
+      </c>
+      <c r="N377" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456551</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B378" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C378" s="6">
+        <v>9893791102</v>
+      </c>
       <c r="D378" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E378" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F378" s="5">
+        <v>47678965772</v>
+      </c>
       <c r="G378" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H378" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I378" t="s">
+        <v>390</v>
+      </c>
+      <c r="K378" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L378">
+        <v>456552</v>
+      </c>
+      <c r="N378" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456552</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B379" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C379" s="6">
+        <v>9893791103</v>
+      </c>
       <c r="D379" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E379" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F379" s="5">
+        <v>47678965773</v>
+      </c>
       <c r="G379" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H379" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I379" t="s">
+        <v>391</v>
+      </c>
+      <c r="K379" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L379">
+        <v>456553</v>
+      </c>
+      <c r="N379" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456553</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C380" s="6">
+        <v>9893791104</v>
+      </c>
       <c r="D380" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E380" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F380" s="5">
+        <v>47678965774</v>
+      </c>
       <c r="G380" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H380" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I380" t="s">
+        <v>392</v>
+      </c>
+      <c r="K380" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L380">
+        <v>456554</v>
+      </c>
+      <c r="N380" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456554</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C381" s="6">
+        <v>9893791105</v>
+      </c>
       <c r="D381" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E381" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F381" s="5">
+        <v>47678965775</v>
+      </c>
       <c r="G381" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H381" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I381" t="s">
+        <v>393</v>
+      </c>
+      <c r="K381" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L381">
+        <v>456555</v>
+      </c>
+      <c r="N381" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456555</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B382" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C382" s="6">
+        <v>9893791106</v>
+      </c>
       <c r="D382" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E382" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F382" s="5">
+        <v>47678965776</v>
+      </c>
       <c r="G382" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H382" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I382" t="s">
+        <v>394</v>
+      </c>
+      <c r="K382" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L382">
+        <v>456556</v>
+      </c>
+      <c r="N382" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456556</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B383" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C383" s="6">
+        <v>9893791107</v>
+      </c>
       <c r="D383" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E383" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F383" s="5">
+        <v>47678965777</v>
+      </c>
       <c r="G383" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H383" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I383" t="s">
+        <v>395</v>
+      </c>
+      <c r="K383" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L383">
+        <v>456557</v>
+      </c>
+      <c r="N383" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456557</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C384" s="6">
+        <v>9893791108</v>
+      </c>
       <c r="D384" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E384" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F384" s="5">
+        <v>47678965778</v>
+      </c>
       <c r="G384" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H384" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I384" t="s">
+        <v>396</v>
+      </c>
+      <c r="K384" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L384">
+        <v>456558</v>
+      </c>
+      <c r="N384" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456558</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B385" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C385" s="6">
+        <v>9893791109</v>
+      </c>
       <c r="D385" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E385" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F385" s="5">
+        <v>47678965779</v>
+      </c>
       <c r="G385" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H385" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I385" t="s">
+        <v>397</v>
+      </c>
+      <c r="K385" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L385">
+        <v>456559</v>
+      </c>
+      <c r="N385" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456559</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B386" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C386" s="6">
+        <v>9893791110</v>
+      </c>
       <c r="D386" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E386" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F386" s="5">
+        <v>47678965780</v>
+      </c>
       <c r="G386" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H386" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I386" t="s">
+        <v>398</v>
+      </c>
+      <c r="K386" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L386">
+        <v>456560</v>
+      </c>
+      <c r="N386" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456560</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B387" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C387" s="6">
+        <v>9893791111</v>
+      </c>
       <c r="D387" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E387" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F387" s="5">
+        <v>47678965781</v>
+      </c>
       <c r="G387" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H387" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I387" t="s">
+        <v>399</v>
+      </c>
+      <c r="K387" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L387">
+        <v>456561</v>
+      </c>
+      <c r="N387" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456561</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B388" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C388" s="6">
+        <v>9893791112</v>
+      </c>
       <c r="D388" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E388" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F388" s="5">
+        <v>47678965782</v>
+      </c>
       <c r="G388" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H388" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I388" t="s">
+        <v>400</v>
+      </c>
+      <c r="K388" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L388">
+        <v>456562</v>
+      </c>
+      <c r="N388" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456562</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B389" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C389" s="6">
+        <v>9893791113</v>
+      </c>
       <c r="D389" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E389" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F389" s="5">
+        <v>47678965783</v>
+      </c>
       <c r="G389" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H389" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I389" t="s">
+        <v>401</v>
+      </c>
+      <c r="K389" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L389">
+        <v>456563</v>
+      </c>
+      <c r="N389" t="str">
+        <f t="shared" ref="N389" si="6">K389&amp;L389</f>
+        <v>GHE456563</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B390" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C390" s="6">
+        <v>9893791114</v>
+      </c>
       <c r="D390" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E390" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F390" s="5">
+        <v>47678965784</v>
+      </c>
       <c r="G390" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H390" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I390" t="s">
+        <v>402</v>
+      </c>
+      <c r="K390" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L390">
+        <v>456564</v>
+      </c>
+      <c r="N390" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456564</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B391" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C391" s="6">
+        <v>9893791115</v>
+      </c>
       <c r="D391" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E391" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F391" s="5">
+        <v>47678965785</v>
+      </c>
       <c r="G391" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H391" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I391" t="s">
+        <v>403</v>
+      </c>
+      <c r="K391" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L391">
+        <v>456565</v>
+      </c>
+      <c r="N391" t="str">
+        <f t="shared" si="5"/>
+        <v>GHE456565</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B392" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C392" s="6">
+        <v>9893791116</v>
+      </c>
       <c r="D392" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E392" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F392" s="5">
+        <v>47678965786</v>
+      </c>
       <c r="G392" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H392" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I392" t="s">
+        <v>404</v>
+      </c>
+      <c r="K392" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L392">
+        <v>456566</v>
+      </c>
+      <c r="N392" t="str">
+        <f t="shared" ref="N392:N455" si="7">K392&amp;L392</f>
+        <v>GHE456566</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C393" s="6">
+        <v>9893791117</v>
+      </c>
       <c r="D393" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E393" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F393" s="5">
+        <v>47678965787</v>
+      </c>
       <c r="G393" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H393" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I393" t="s">
+        <v>405</v>
+      </c>
+      <c r="K393" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L393">
+        <v>456567</v>
+      </c>
+      <c r="N393" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456567</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B394" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C394" s="6">
+        <v>9893791118</v>
+      </c>
       <c r="D394" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E394" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F394" s="5">
+        <v>47678965788</v>
+      </c>
       <c r="G394" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H394" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I394" t="s">
+        <v>406</v>
+      </c>
+      <c r="K394" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L394">
+        <v>456568</v>
+      </c>
+      <c r="N394" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456568</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B395" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C395" s="6">
+        <v>9893791119</v>
+      </c>
       <c r="D395" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E395" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F395" s="5">
+        <v>47678965789</v>
+      </c>
       <c r="G395" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H395" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I395" t="s">
+        <v>407</v>
+      </c>
+      <c r="K395" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L395">
+        <v>456569</v>
+      </c>
+      <c r="N395" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456569</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B396" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C396" s="6">
+        <v>9893791120</v>
+      </c>
       <c r="D396" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E396" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F396" s="5">
+        <v>47678965790</v>
+      </c>
       <c r="G396" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H396" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I396" t="s">
+        <v>408</v>
+      </c>
+      <c r="K396" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L396">
+        <v>456570</v>
+      </c>
+      <c r="N396" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456570</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B397" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C397" s="6">
+        <v>9893791121</v>
+      </c>
       <c r="D397" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E397" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F397" s="5">
+        <v>47678965791</v>
+      </c>
       <c r="G397" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H397" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I397" t="s">
+        <v>409</v>
+      </c>
+      <c r="K397" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L397">
+        <v>456571</v>
+      </c>
+      <c r="N397" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456571</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B398" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C398" s="6">
+        <v>9893791122</v>
+      </c>
       <c r="D398" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E398" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F398" s="5">
+        <v>47678965792</v>
+      </c>
       <c r="G398" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H398" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I398" t="s">
+        <v>410</v>
+      </c>
+      <c r="K398" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L398">
+        <v>456572</v>
+      </c>
+      <c r="N398" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456572</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B399" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C399" s="6">
+        <v>9893791123</v>
+      </c>
       <c r="D399" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E399" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F399" s="5">
+        <v>47678965793</v>
+      </c>
       <c r="G399" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H399" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I399" t="s">
+        <v>411</v>
+      </c>
+      <c r="K399" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L399">
+        <v>456573</v>
+      </c>
+      <c r="N399" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456573</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B400" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C400" s="6">
+        <v>9893791124</v>
+      </c>
       <c r="D400" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E400" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F400" s="5">
+        <v>47678965794</v>
+      </c>
       <c r="G400" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H400" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I400" t="s">
+        <v>412</v>
+      </c>
+      <c r="K400" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L400">
+        <v>456574</v>
+      </c>
+      <c r="N400" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456574</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A401" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B401" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C401" s="6">
+        <v>9893791125</v>
+      </c>
       <c r="D401" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E401" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F401" s="5">
+        <v>47678965795</v>
+      </c>
       <c r="G401" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H401" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I401" t="s">
+        <v>413</v>
+      </c>
+      <c r="K401" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L401">
+        <v>456575</v>
+      </c>
+      <c r="N401" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456575</v>
+      </c>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A402" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B402" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C402" s="6">
+        <v>9893791126</v>
+      </c>
       <c r="D402" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E402" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F402" s="5">
+        <v>47678965796</v>
+      </c>
       <c r="G402" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H402" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I402" t="s">
+        <v>414</v>
+      </c>
+      <c r="K402" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L402">
+        <v>456576</v>
+      </c>
+      <c r="N402" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456576</v>
+      </c>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A403" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B403" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C403" s="6">
+        <v>9893791127</v>
+      </c>
       <c r="D403" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E403" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F403" s="5">
+        <v>47678965797</v>
+      </c>
       <c r="G403" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H403" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I403" t="s">
+        <v>415</v>
+      </c>
+      <c r="K403" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L403">
+        <v>456577</v>
+      </c>
+      <c r="N403" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456577</v>
+      </c>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A404" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B404" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C404" s="6">
+        <v>9893791128</v>
+      </c>
       <c r="D404" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E404" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F404" s="5">
+        <v>47678965798</v>
+      </c>
       <c r="G404" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H404" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I404" t="s">
+        <v>416</v>
+      </c>
+      <c r="K404" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L404">
+        <v>456578</v>
+      </c>
+      <c r="N404" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456578</v>
+      </c>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A405" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B405" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C405" s="6">
+        <v>9893791129</v>
+      </c>
       <c r="D405" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E405" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F405" s="5">
+        <v>47678965799</v>
+      </c>
       <c r="G405" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H405" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I405" t="s">
+        <v>417</v>
+      </c>
+      <c r="K405" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L405">
+        <v>456579</v>
+      </c>
+      <c r="N405" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456579</v>
+      </c>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A406" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C406" s="6">
+        <v>9893791130</v>
+      </c>
       <c r="D406" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E406" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F406" s="5">
+        <v>47678965800</v>
+      </c>
       <c r="G406" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H406" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I406" t="s">
+        <v>418</v>
+      </c>
+      <c r="K406" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L406">
+        <v>456580</v>
+      </c>
+      <c r="N406" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456580</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A407" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C407" s="6">
+        <v>9893791131</v>
+      </c>
       <c r="D407" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E407" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F407" s="5">
+        <v>47678965801</v>
+      </c>
       <c r="G407" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H407" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I407" t="s">
+        <v>419</v>
+      </c>
+      <c r="K407" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L407">
+        <v>456581</v>
+      </c>
+      <c r="N407" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456581</v>
+      </c>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A408" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B408" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C408" s="6">
+        <v>9893791132</v>
+      </c>
       <c r="D408" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E408" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F408" s="5">
+        <v>47678965802</v>
+      </c>
       <c r="G408" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H408" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I408" t="s">
+        <v>420</v>
+      </c>
+      <c r="K408" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L408">
+        <v>456582</v>
+      </c>
+      <c r="N408" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456582</v>
+      </c>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A409" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B409" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C409" s="6">
+        <v>9893791133</v>
+      </c>
       <c r="D409" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E409" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F409" s="5">
+        <v>47678965803</v>
+      </c>
       <c r="G409" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H409" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I409" t="s">
+        <v>421</v>
+      </c>
+      <c r="K409" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L409">
+        <v>456583</v>
+      </c>
+      <c r="N409" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456583</v>
+      </c>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A410" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B410" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C410" s="6">
+        <v>9893791134</v>
+      </c>
       <c r="D410" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E410" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F410" s="5">
+        <v>47678965804</v>
+      </c>
       <c r="G410" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H410" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I410" t="s">
+        <v>422</v>
+      </c>
+      <c r="K410" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L410">
+        <v>456584</v>
+      </c>
+      <c r="N410" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456584</v>
+      </c>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C411" s="6">
+        <v>9893791135</v>
+      </c>
       <c r="D411" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E411" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F411" s="5">
+        <v>47678965805</v>
+      </c>
       <c r="G411" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H411" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I411" t="s">
+        <v>423</v>
+      </c>
+      <c r="K411" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L411">
+        <v>456585</v>
+      </c>
+      <c r="N411" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456585</v>
+      </c>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A412" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C412" s="6">
+        <v>9893791136</v>
+      </c>
       <c r="D412" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E412" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F412" s="5">
+        <v>47678965806</v>
+      </c>
       <c r="G412" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H412" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I412" t="s">
+        <v>424</v>
+      </c>
+      <c r="K412" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L412">
+        <v>456586</v>
+      </c>
+      <c r="N412" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456586</v>
+      </c>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A413" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B413" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C413" s="6">
+        <v>9893791137</v>
+      </c>
       <c r="D413" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E413" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F413" s="5">
+        <v>47678965807</v>
+      </c>
       <c r="G413" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H413" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I413" t="s">
+        <v>425</v>
+      </c>
+      <c r="K413" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L413">
+        <v>456587</v>
+      </c>
+      <c r="N413" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456587</v>
+      </c>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A414" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B414" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C414" s="6">
+        <v>9893791138</v>
+      </c>
       <c r="D414" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E414" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F414" s="5">
+        <v>47678965808</v>
+      </c>
       <c r="G414" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H414" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I414" t="s">
+        <v>426</v>
+      </c>
+      <c r="K414" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L414">
+        <v>456588</v>
+      </c>
+      <c r="N414" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456588</v>
+      </c>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A415" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C415" s="6">
+        <v>9893791139</v>
+      </c>
       <c r="D415" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E415" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F415" s="5">
+        <v>47678965809</v>
+      </c>
       <c r="G415" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H415" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I415" t="s">
+        <v>427</v>
+      </c>
+      <c r="K415" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L415">
+        <v>456589</v>
+      </c>
+      <c r="N415" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456589</v>
+      </c>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A416" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B416" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C416" s="6">
+        <v>9893791140</v>
+      </c>
       <c r="D416" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E416" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F416" s="5">
+        <v>47678965810</v>
+      </c>
       <c r="G416" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H416" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I416" t="s">
+        <v>428</v>
+      </c>
+      <c r="K416" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L416">
+        <v>456590</v>
+      </c>
+      <c r="N416" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456590</v>
+      </c>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A417" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B417" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C417" s="6">
+        <v>9893791141</v>
+      </c>
       <c r="D417" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E417" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F417" s="5">
+        <v>47678965811</v>
+      </c>
       <c r="G417" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H417" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I417" t="s">
+        <v>429</v>
+      </c>
+      <c r="K417" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L417">
+        <v>456591</v>
+      </c>
+      <c r="N417" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456591</v>
+      </c>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A418" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B418" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C418" s="6">
+        <v>9893791142</v>
+      </c>
       <c r="D418" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E418" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F418" s="5">
+        <v>47678965812</v>
+      </c>
       <c r="G418" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H418" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I418" t="s">
+        <v>430</v>
+      </c>
+      <c r="K418" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L418">
+        <v>456592</v>
+      </c>
+      <c r="N418" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456592</v>
+      </c>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A419" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B419" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C419" s="6">
+        <v>9893791143</v>
+      </c>
       <c r="D419" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E419" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F419" s="5">
+        <v>47678965813</v>
+      </c>
       <c r="G419" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H419" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I419" t="s">
+        <v>431</v>
+      </c>
+      <c r="K419" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L419">
+        <v>456593</v>
+      </c>
+      <c r="N419" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456593</v>
+      </c>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A420" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B420" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C420" s="6">
+        <v>9893791144</v>
+      </c>
       <c r="D420" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E420" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F420" s="5">
+        <v>47678965814</v>
+      </c>
       <c r="G420" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H420" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I420" t="s">
+        <v>432</v>
+      </c>
+      <c r="K420" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L420">
+        <v>456594</v>
+      </c>
+      <c r="N420" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456594</v>
+      </c>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B421" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C421" s="6">
+        <v>9893791145</v>
+      </c>
       <c r="D421" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E421" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F421" s="5">
+        <v>47678965815</v>
+      </c>
       <c r="G421" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H421" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I421" t="s">
+        <v>433</v>
+      </c>
+      <c r="K421" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L421">
+        <v>456595</v>
+      </c>
+      <c r="N421" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456595</v>
+      </c>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A422" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B422" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C422" s="6">
+        <v>9893791146</v>
+      </c>
       <c r="D422" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E422" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F422" s="5">
+        <v>47678965816</v>
+      </c>
       <c r="G422" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H422" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I422" t="s">
+        <v>434</v>
+      </c>
+      <c r="K422" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L422">
+        <v>456596</v>
+      </c>
+      <c r="N422" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456596</v>
+      </c>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A423" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B423" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C423" s="6">
+        <v>9893791147</v>
+      </c>
       <c r="D423" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E423" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F423" s="5">
+        <v>47678965817</v>
+      </c>
       <c r="G423" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H423" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I423" t="s">
+        <v>435</v>
+      </c>
+      <c r="K423" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L423">
+        <v>456597</v>
+      </c>
+      <c r="N423" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456597</v>
+      </c>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A424" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B424" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C424" s="6">
+        <v>9893791148</v>
+      </c>
       <c r="D424" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E424" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F424" s="5">
+        <v>47678965818</v>
+      </c>
       <c r="G424" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H424" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I424" t="s">
+        <v>436</v>
+      </c>
+      <c r="K424" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L424">
+        <v>456598</v>
+      </c>
+      <c r="N424" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456598</v>
+      </c>
+    </row>
+    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A425" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B425" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C425" s="6">
+        <v>9893791149</v>
+      </c>
       <c r="D425" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E425" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F425" s="5">
+        <v>47678965819</v>
+      </c>
       <c r="G425" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H425" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I425" t="s">
+        <v>437</v>
+      </c>
+      <c r="K425" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L425">
+        <v>456599</v>
+      </c>
+      <c r="N425" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456599</v>
+      </c>
+    </row>
+    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A426" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B426" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C426" s="6">
+        <v>9893791150</v>
+      </c>
       <c r="D426" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E426" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F426" s="5">
+        <v>47678965820</v>
+      </c>
       <c r="G426" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H426" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I426" t="s">
+        <v>438</v>
+      </c>
+      <c r="K426" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L426">
+        <v>456600</v>
+      </c>
+      <c r="N426" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456600</v>
+      </c>
+    </row>
+    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A427" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B427" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C427" s="6">
+        <v>9893791151</v>
+      </c>
       <c r="D427" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E427" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F427" s="5">
+        <v>47678965821</v>
+      </c>
       <c r="G427" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H427" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I427" t="s">
+        <v>439</v>
+      </c>
+      <c r="K427" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L427">
+        <v>456601</v>
+      </c>
+      <c r="N427" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456601</v>
+      </c>
+    </row>
+    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A428" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B428" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C428" s="6">
+        <v>9893791152</v>
+      </c>
       <c r="D428" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E428" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F428" s="5">
+        <v>47678965822</v>
+      </c>
       <c r="G428" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H428" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I428" t="s">
+        <v>440</v>
+      </c>
+      <c r="K428" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L428">
+        <v>456602</v>
+      </c>
+      <c r="N428" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456602</v>
+      </c>
+    </row>
+    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A429" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B429" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C429" s="6">
+        <v>9893791153</v>
+      </c>
       <c r="D429" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E429" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F429" s="5">
+        <v>47678965823</v>
+      </c>
       <c r="G429" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H429" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I429" t="s">
+        <v>441</v>
+      </c>
+      <c r="K429" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L429">
+        <v>456603</v>
+      </c>
+      <c r="N429" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456603</v>
+      </c>
+    </row>
+    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A430" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B430" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C430" s="6">
+        <v>9893791154</v>
+      </c>
       <c r="D430" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E430" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F430" s="5">
+        <v>47678965824</v>
+      </c>
       <c r="G430" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H430" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I430" t="s">
+        <v>442</v>
+      </c>
+      <c r="K430" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L430">
+        <v>456604</v>
+      </c>
+      <c r="N430" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456604</v>
+      </c>
+    </row>
+    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B431" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C431" s="6">
+        <v>9893791155</v>
+      </c>
       <c r="D431" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E431" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F431" s="5">
+        <v>47678965825</v>
+      </c>
       <c r="G431" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H431" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I431" t="s">
+        <v>443</v>
+      </c>
+      <c r="K431" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L431">
+        <v>456605</v>
+      </c>
+      <c r="N431" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456605</v>
+      </c>
+    </row>
+    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A432" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B432" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C432" s="6">
+        <v>9893791156</v>
+      </c>
       <c r="D432" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E432" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F432" s="5">
+        <v>47678965826</v>
+      </c>
       <c r="G432" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H432" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I432" t="s">
+        <v>444</v>
+      </c>
+      <c r="K432" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L432">
+        <v>456606</v>
+      </c>
+      <c r="N432" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456606</v>
+      </c>
+    </row>
+    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A433" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B433" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C433" s="6">
+        <v>9893791157</v>
+      </c>
       <c r="D433" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E433" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F433" s="5">
+        <v>47678965827</v>
+      </c>
       <c r="G433" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H433" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I433" t="s">
+        <v>445</v>
+      </c>
+      <c r="K433" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L433">
+        <v>456607</v>
+      </c>
+      <c r="N433" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456607</v>
+      </c>
+    </row>
+    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A434" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C434" s="6">
+        <v>9893791158</v>
+      </c>
       <c r="D434" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E434" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F434" s="5">
+        <v>47678965828</v>
+      </c>
       <c r="G434" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H434" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I434" t="s">
+        <v>446</v>
+      </c>
+      <c r="K434" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L434">
+        <v>456608</v>
+      </c>
+      <c r="N434" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456608</v>
+      </c>
+    </row>
+    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A435" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B435" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C435" s="6">
+        <v>9893791159</v>
+      </c>
       <c r="D435" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E435" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F435" s="5">
+        <v>47678965829</v>
+      </c>
       <c r="G435" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H435" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I435" t="s">
+        <v>447</v>
+      </c>
+      <c r="K435" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L435">
+        <v>456609</v>
+      </c>
+      <c r="N435" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456609</v>
+      </c>
+    </row>
+    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A436" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B436" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C436" s="6">
+        <v>9893791160</v>
+      </c>
       <c r="D436" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E436" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F436" s="5">
+        <v>47678965830</v>
+      </c>
       <c r="G436" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H436" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I436" t="s">
+        <v>448</v>
+      </c>
+      <c r="K436" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L436">
+        <v>456610</v>
+      </c>
+      <c r="N436" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456610</v>
+      </c>
+    </row>
+    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A437" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B437" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C437" s="6">
+        <v>9893791161</v>
+      </c>
       <c r="D437" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E437" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F437" s="5">
+        <v>47678965831</v>
+      </c>
       <c r="G437" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H437" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I437" t="s">
+        <v>449</v>
+      </c>
+      <c r="K437" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L437">
+        <v>456611</v>
+      </c>
+      <c r="N437" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456611</v>
+      </c>
+    </row>
+    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A438" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B438" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C438" s="6">
+        <v>9893791162</v>
+      </c>
       <c r="D438" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E438" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F438" s="5">
+        <v>47678965832</v>
+      </c>
       <c r="G438" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H438" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I438" t="s">
+        <v>450</v>
+      </c>
+      <c r="K438" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L438">
+        <v>456612</v>
+      </c>
+      <c r="N438" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456612</v>
+      </c>
+    </row>
+    <row r="439" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A439" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B439" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C439" s="6">
+        <v>9893791163</v>
+      </c>
       <c r="D439" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E439" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F439" s="5">
+        <v>47678965833</v>
+      </c>
       <c r="G439" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H439" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I439" t="s">
+        <v>451</v>
+      </c>
+      <c r="K439" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L439">
+        <v>456613</v>
+      </c>
+      <c r="N439" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456613</v>
+      </c>
+    </row>
+    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A440" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C440" s="6">
+        <v>9893791164</v>
+      </c>
       <c r="D440" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E440" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F440" s="5">
+        <v>47678965834</v>
+      </c>
       <c r="G440" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H440" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I440" t="s">
+        <v>452</v>
+      </c>
+      <c r="K440" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L440">
+        <v>456614</v>
+      </c>
+      <c r="N440" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456614</v>
+      </c>
+    </row>
+    <row r="441" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A441" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B441" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C441" s="6">
+        <v>9893791165</v>
+      </c>
       <c r="D441" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E441" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F441" s="5">
+        <v>47678965835</v>
+      </c>
       <c r="G441" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H441" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I441" t="s">
+        <v>453</v>
+      </c>
+      <c r="K441" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L441">
+        <v>456615</v>
+      </c>
+      <c r="N441" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456615</v>
+      </c>
+    </row>
+    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A442" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B442" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C442" s="6">
+        <v>9893791166</v>
+      </c>
       <c r="D442" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E442" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F442" s="5">
+        <v>47678965836</v>
+      </c>
       <c r="G442" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H442" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I442" t="s">
+        <v>454</v>
+      </c>
+      <c r="K442" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L442">
+        <v>456616</v>
+      </c>
+      <c r="N442" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456616</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A443" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B443" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C443" s="6">
+        <v>9893791167</v>
+      </c>
       <c r="D443" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E443" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F443" s="5">
+        <v>47678965837</v>
+      </c>
       <c r="G443" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H443" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I443" t="s">
+        <v>455</v>
+      </c>
+      <c r="K443" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L443">
+        <v>456617</v>
+      </c>
+      <c r="N443" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456617</v>
+      </c>
+    </row>
+    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C444" s="6">
+        <v>9893791168</v>
+      </c>
       <c r="D444" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E444" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F444" s="5">
+        <v>47678965838</v>
+      </c>
       <c r="G444" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H444" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I444" t="s">
+        <v>456</v>
+      </c>
+      <c r="K444" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L444">
+        <v>456618</v>
+      </c>
+      <c r="N444" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456618</v>
+      </c>
+    </row>
+    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A445" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C445" s="6">
+        <v>9893791169</v>
+      </c>
       <c r="D445" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E445" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F445" s="5">
+        <v>47678965839</v>
+      </c>
       <c r="G445" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H445" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I445" t="s">
+        <v>457</v>
+      </c>
+      <c r="K445" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L445">
+        <v>456619</v>
+      </c>
+      <c r="N445" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456619</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A446" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C446" s="6">
+        <v>9893791170</v>
+      </c>
       <c r="D446" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E446" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F446" s="5">
+        <v>47678965840</v>
+      </c>
       <c r="G446" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H446" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I446" t="s">
+        <v>458</v>
+      </c>
+      <c r="K446" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L446">
+        <v>456620</v>
+      </c>
+      <c r="N446" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456620</v>
+      </c>
+    </row>
+    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A447" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B447" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C447" s="6">
+        <v>9893791171</v>
+      </c>
       <c r="D447" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E447" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F447" s="5">
+        <v>47678965841</v>
+      </c>
       <c r="G447" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H447" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I447" t="s">
+        <v>459</v>
+      </c>
+      <c r="K447" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L447">
+        <v>456621</v>
+      </c>
+      <c r="N447" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456621</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B448" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C448" s="6">
+        <v>9893791172</v>
+      </c>
       <c r="D448" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E448" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F448" s="5">
+        <v>47678965842</v>
+      </c>
       <c r="G448" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H448" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I448" t="s">
+        <v>460</v>
+      </c>
+      <c r="K448" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L448">
+        <v>456622</v>
+      </c>
+      <c r="N448" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456622</v>
+      </c>
+    </row>
+    <row r="449" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C449" s="6">
+        <v>9893791173</v>
+      </c>
       <c r="D449" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E449" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F449" s="5">
+        <v>47678965843</v>
+      </c>
       <c r="G449" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H449" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I449" t="s">
+        <v>461</v>
+      </c>
+      <c r="K449" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L449">
+        <v>456623</v>
+      </c>
+      <c r="N449" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456623</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B450" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C450" s="6">
+        <v>9893791174</v>
+      </c>
       <c r="D450" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E450" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="F450" s="5">
+        <v>47678965844</v>
+      </c>
       <c r="G450" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H450" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="I450" t="s">
+        <v>462</v>
+      </c>
+      <c r="K450" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L450">
+        <v>456624</v>
+      </c>
+      <c r="N450" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456624</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A451" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B451" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C451" s="6">
+        <v>9893791175</v>
+      </c>
+      <c r="D451" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E451" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F451" s="5">
+        <v>47678965845</v>
+      </c>
+      <c r="G451" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H451" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I451" t="s">
+        <v>463</v>
+      </c>
+      <c r="K451" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L451">
+        <v>456625</v>
+      </c>
+      <c r="N451" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456625</v>
+      </c>
+    </row>
+    <row r="452" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A452" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B452" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C452" s="6">
+        <v>9893791176</v>
+      </c>
+      <c r="D452" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E452" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F452" s="5">
+        <v>47678965846</v>
+      </c>
+      <c r="G452" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H452" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I452" t="s">
+        <v>464</v>
+      </c>
+      <c r="K452" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L452">
+        <v>456626</v>
+      </c>
+      <c r="N452" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456626</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A453" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C453" s="6">
+        <v>9893791177</v>
+      </c>
+      <c r="D453" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E453" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F453" s="5">
+        <v>47678965847</v>
+      </c>
+      <c r="G453" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H453" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I453" t="s">
+        <v>465</v>
+      </c>
+      <c r="K453" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L453">
+        <v>456627</v>
+      </c>
+      <c r="N453" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456627</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A454" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C454" s="6">
+        <v>9893791178</v>
+      </c>
+      <c r="D454" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E454" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F454" s="5">
+        <v>47678965848</v>
+      </c>
+      <c r="G454" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H454" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I454" t="s">
+        <v>466</v>
+      </c>
+      <c r="K454" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L454">
+        <v>456628</v>
+      </c>
+      <c r="N454" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456628</v>
+      </c>
+    </row>
+    <row r="455" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A455" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B455" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C455" s="6">
+        <v>9893791179</v>
+      </c>
+      <c r="D455" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E455" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F455" s="5">
+        <v>47678965849</v>
+      </c>
+      <c r="G455" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H455" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I455" t="s">
+        <v>467</v>
+      </c>
+      <c r="K455" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L455">
+        <v>456629</v>
+      </c>
+      <c r="N455" t="str">
+        <f t="shared" si="7"/>
+        <v>GHE456629</v>
+      </c>
+    </row>
+    <row r="456" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A456" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B456" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C456" s="6">
+        <v>9893791180</v>
+      </c>
+      <c r="D456" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E456" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F456" s="5">
+        <v>47678965850</v>
+      </c>
+      <c r="G456" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H456" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I456" t="s">
+        <v>468</v>
+      </c>
+      <c r="K456" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L456">
+        <v>456630</v>
+      </c>
+      <c r="N456" t="str">
+        <f t="shared" ref="N456:N461" si="8">K456&amp;L456</f>
+        <v>GHE456630</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A457" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B457" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C457" s="6">
+        <v>9893791181</v>
+      </c>
+      <c r="D457" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E457" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F457" s="5">
+        <v>47678965851</v>
+      </c>
+      <c r="G457" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H457" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I457" t="s">
+        <v>469</v>
+      </c>
+      <c r="K457" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L457">
+        <v>456631</v>
+      </c>
+      <c r="N457" t="str">
+        <f t="shared" si="8"/>
+        <v>GHE456631</v>
+      </c>
+    </row>
+    <row r="458" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A458" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C458" s="6">
+        <v>9893791182</v>
+      </c>
+      <c r="D458" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E458" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F458" s="5">
+        <v>47678965852</v>
+      </c>
+      <c r="G458" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H458" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I458" t="s">
+        <v>470</v>
+      </c>
+      <c r="K458" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L458">
+        <v>456632</v>
+      </c>
+      <c r="N458" t="str">
+        <f t="shared" si="8"/>
+        <v>GHE456632</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A459" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C459" s="6">
+        <v>9893791183</v>
+      </c>
+      <c r="D459" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E459" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F459" s="5">
+        <v>47678965853</v>
+      </c>
+      <c r="G459" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H459" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I459" t="s">
+        <v>471</v>
+      </c>
+      <c r="K459" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L459">
+        <v>456633</v>
+      </c>
+      <c r="N459" t="str">
+        <f t="shared" si="8"/>
+        <v>GHE456633</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A460" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B460" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C460" s="6">
+        <v>9893791184</v>
+      </c>
+      <c r="D460" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E460" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F460" s="5">
+        <v>47678965854</v>
+      </c>
+      <c r="G460" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H460" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I460" t="s">
+        <v>472</v>
+      </c>
+      <c r="K460" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L460">
+        <v>456634</v>
+      </c>
+      <c r="N460" t="str">
+        <f t="shared" si="8"/>
+        <v>GHE456634</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A461" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B461" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C461" s="6">
+        <v>9893791185</v>
+      </c>
+      <c r="D461" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E461" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F461" s="5">
+        <v>47678965855</v>
+      </c>
+      <c r="G461" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H461" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I461" t="s">
+        <v>473</v>
+      </c>
+      <c r="K461" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L461">
+        <v>456635</v>
+      </c>
+      <c r="N461" t="str">
+        <f t="shared" si="8"/>
+        <v>GHE456635</v>
       </c>
     </row>
   </sheetData>
